--- a/AAII_Financials/Yearly/XP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/XP_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="92">
   <si>
     <t>XP</t>
   </si>
@@ -656,55 +656,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
@@ -714,36 +714,39 @@
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>2744600</v>
+        <v>2978400</v>
       </c>
       <c r="E8" s="3">
-        <v>2483400</v>
+        <v>2675100</v>
       </c>
       <c r="F8" s="3">
-        <v>1676200</v>
+        <v>2420500</v>
       </c>
       <c r="G8" s="3">
-        <v>1054400</v>
+        <v>1633700</v>
       </c>
       <c r="H8" s="3">
-        <v>608300</v>
+        <v>1027700</v>
       </c>
       <c r="I8" s="3">
-        <v>392100</v>
+        <v>592900</v>
       </c>
       <c r="J8" s="3">
+        <v>382100</v>
+      </c>
+      <c r="K8" s="3">
         <v>257400</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
@@ -753,9 +756,12 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -792,9 +798,12 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -831,9 +840,12 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -849,8 +861,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -887,9 +900,12 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,23 +942,26 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>1400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>900</v>
       </c>
-      <c r="F14" s="3">
-        <v>10700</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3">
+        <v>10400</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -959,42 +978,45 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>42300</v>
+      <c r="D15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E15" s="3">
-        <v>47700</v>
+        <v>41300</v>
       </c>
       <c r="F15" s="3">
-        <v>29500</v>
+        <v>46400</v>
       </c>
       <c r="G15" s="3">
-        <v>18700</v>
+        <v>28700</v>
       </c>
       <c r="H15" s="3">
-        <v>10900</v>
+        <v>18300</v>
       </c>
       <c r="I15" s="3">
-        <v>5600</v>
+        <v>10600</v>
       </c>
       <c r="J15" s="3">
+        <v>5500</v>
+      </c>
+      <c r="K15" s="3">
         <v>4700</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1004,9 +1026,12 @@
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1019,35 +1044,36 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1951100</v>
+        <v>2080400</v>
       </c>
       <c r="E17" s="3">
-        <v>1669400</v>
+        <v>1901600</v>
       </c>
       <c r="F17" s="3">
-        <v>1167600</v>
+        <v>1627100</v>
       </c>
       <c r="G17" s="3">
-        <v>719600</v>
+        <v>1138100</v>
       </c>
       <c r="H17" s="3">
-        <v>461700</v>
+        <v>701300</v>
       </c>
       <c r="I17" s="3">
-        <v>261200</v>
+        <v>450000</v>
       </c>
       <c r="J17" s="3">
+        <v>254500</v>
+      </c>
+      <c r="K17" s="3">
         <v>180500</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1057,36 +1083,39 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>793600</v>
+        <v>898100</v>
       </c>
       <c r="E18" s="3">
-        <v>814000</v>
+        <v>773400</v>
       </c>
       <c r="F18" s="3">
-        <v>508600</v>
+        <v>793400</v>
       </c>
       <c r="G18" s="3">
-        <v>334900</v>
+        <v>495700</v>
       </c>
       <c r="H18" s="3">
-        <v>146600</v>
+        <v>326400</v>
       </c>
       <c r="I18" s="3">
-        <v>130900</v>
+        <v>142900</v>
       </c>
       <c r="J18" s="3">
+        <v>127600</v>
+      </c>
+      <c r="K18" s="3">
         <v>76900</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1096,9 +1125,12 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1114,34 +1146,35 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2500</v>
+        <v>14400</v>
       </c>
       <c r="E20" s="3">
-        <v>-1600</v>
+        <v>-2400</v>
       </c>
       <c r="F20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
-        <v>-14900</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>-12600</v>
+        <v>-14500</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
+        <v>-12200</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
@@ -1152,36 +1185,39 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>833400</v>
+      <c r="D21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E21" s="3">
-        <v>860100</v>
+        <v>812400</v>
       </c>
       <c r="F21" s="3">
-        <v>538200</v>
+        <v>838500</v>
       </c>
       <c r="G21" s="3">
-        <v>353500</v>
+        <v>524700</v>
       </c>
       <c r="H21" s="3">
-        <v>142600</v>
+        <v>344600</v>
       </c>
       <c r="I21" s="3">
-        <v>124000</v>
+        <v>139000</v>
       </c>
       <c r="J21" s="3">
+        <v>120900</v>
+      </c>
+      <c r="K21" s="3">
         <v>81600</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1191,26 +1227,29 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>82700</v>
+        <v>123700</v>
       </c>
       <c r="E22" s="3">
-        <v>27900</v>
+        <v>80600</v>
       </c>
       <c r="F22" s="3">
-        <v>10800</v>
+        <v>27200</v>
       </c>
       <c r="G22" s="3">
-        <v>17400</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
+        <v>10600</v>
+      </c>
+      <c r="H22" s="3">
+        <v>16900</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
@@ -1227,39 +1266,42 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>708300</v>
+        <v>788900</v>
       </c>
       <c r="E23" s="3">
-        <v>784500</v>
+        <v>690400</v>
       </c>
       <c r="F23" s="3">
-        <v>497900</v>
+        <v>764600</v>
       </c>
       <c r="G23" s="3">
-        <v>317500</v>
+        <v>485300</v>
       </c>
       <c r="H23" s="3">
-        <v>131800</v>
+        <v>309500</v>
       </c>
       <c r="I23" s="3">
-        <v>118300</v>
+        <v>128400</v>
       </c>
       <c r="J23" s="3">
+        <v>115300</v>
+      </c>
+      <c r="K23" s="3">
         <v>76900</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1269,36 +1311,39 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-27900</v>
+        <v>7400</v>
       </c>
       <c r="E24" s="3">
-        <v>45800</v>
+        <v>-27200</v>
       </c>
       <c r="F24" s="3">
-        <v>69900</v>
+        <v>44600</v>
       </c>
       <c r="G24" s="3">
-        <v>93500</v>
+        <v>68100</v>
       </c>
       <c r="H24" s="3">
-        <v>36100</v>
+        <v>91100</v>
       </c>
       <c r="I24" s="3">
-        <v>31200</v>
+        <v>35200</v>
       </c>
       <c r="J24" s="3">
+        <v>30500</v>
+      </c>
+      <c r="K24" s="3">
         <v>26800</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1308,9 +1353,12 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1347,36 +1395,39 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>736200</v>
+        <v>781400</v>
       </c>
       <c r="E26" s="3">
-        <v>738700</v>
+        <v>717500</v>
       </c>
       <c r="F26" s="3">
-        <v>428000</v>
+        <v>720000</v>
       </c>
       <c r="G26" s="3">
-        <v>224000</v>
+        <v>417200</v>
       </c>
       <c r="H26" s="3">
-        <v>95700</v>
+        <v>218400</v>
       </c>
       <c r="I26" s="3">
-        <v>87100</v>
+        <v>93300</v>
       </c>
       <c r="J26" s="3">
+        <v>84900</v>
+      </c>
+      <c r="K26" s="3">
         <v>50100</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1386,36 +1437,39 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>736000</v>
+        <v>781400</v>
       </c>
       <c r="E27" s="3">
-        <v>738100</v>
+        <v>717300</v>
       </c>
       <c r="F27" s="3">
-        <v>427000</v>
+        <v>719400</v>
       </c>
       <c r="G27" s="3">
-        <v>222200</v>
+        <v>416200</v>
       </c>
       <c r="H27" s="3">
-        <v>94900</v>
+        <v>216600</v>
       </c>
       <c r="I27" s="3">
-        <v>85100</v>
+        <v>92500</v>
       </c>
       <c r="J27" s="3">
+        <v>82900</v>
+      </c>
+      <c r="K27" s="3">
         <v>38800</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1425,9 +1479,12 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1464,9 +1521,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1503,9 +1563,12 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1542,9 +1605,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1581,35 +1647,38 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2500</v>
+        <v>-14400</v>
       </c>
       <c r="E32" s="3">
-        <v>1600</v>
+        <v>2400</v>
       </c>
       <c r="F32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
-        <v>14900</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>12600</v>
+        <v>14500</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
+        <v>12200</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
@@ -1620,36 +1689,39 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>736000</v>
+        <v>781400</v>
       </c>
       <c r="E33" s="3">
-        <v>738100</v>
+        <v>717300</v>
       </c>
       <c r="F33" s="3">
-        <v>427000</v>
+        <v>719400</v>
       </c>
       <c r="G33" s="3">
-        <v>222200</v>
+        <v>416200</v>
       </c>
       <c r="H33" s="3">
-        <v>94900</v>
+        <v>216600</v>
       </c>
       <c r="I33" s="3">
-        <v>85100</v>
+        <v>92500</v>
       </c>
       <c r="J33" s="3">
+        <v>82900</v>
+      </c>
+      <c r="K33" s="3">
         <v>38800</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1659,9 +1731,12 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1698,36 +1773,39 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>736000</v>
+        <v>781400</v>
       </c>
       <c r="E35" s="3">
-        <v>738100</v>
+        <v>717300</v>
       </c>
       <c r="F35" s="3">
-        <v>427000</v>
+        <v>719400</v>
       </c>
       <c r="G35" s="3">
-        <v>222200</v>
+        <v>416200</v>
       </c>
       <c r="H35" s="3">
-        <v>94900</v>
+        <v>216600</v>
       </c>
       <c r="I35" s="3">
-        <v>85100</v>
+        <v>92500</v>
       </c>
       <c r="J35" s="3">
+        <v>82900</v>
+      </c>
+      <c r="K35" s="3">
         <v>38800</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1737,41 +1815,44 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1781,9 +1862,12 @@
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1799,8 +1883,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1816,31 +1901,32 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>730600</v>
+        <v>790300</v>
       </c>
       <c r="E41" s="3">
-        <v>511100</v>
+        <v>712100</v>
       </c>
       <c r="F41" s="3">
-        <v>402000</v>
+        <v>498200</v>
       </c>
       <c r="G41" s="3">
-        <v>22600</v>
+        <v>391800</v>
       </c>
       <c r="H41" s="3">
-        <v>14100</v>
+        <v>22000</v>
       </c>
       <c r="I41" s="3">
-        <v>31500</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+        <v>13700</v>
+      </c>
+      <c r="J41" s="3">
+        <v>30700</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1854,9 +1940,12 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1893,32 +1982,35 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>156500</v>
+        <v>185600</v>
       </c>
       <c r="E43" s="3">
-        <v>128000</v>
+        <v>152500</v>
       </c>
       <c r="F43" s="3">
-        <v>130400</v>
+        <v>124700</v>
       </c>
       <c r="G43" s="3">
-        <v>145000</v>
+        <v>127100</v>
       </c>
       <c r="H43" s="3">
-        <v>82800</v>
+        <v>141400</v>
       </c>
       <c r="I43" s="3">
-        <v>35300</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+        <v>80700</v>
+      </c>
+      <c r="J43" s="3">
+        <v>34400</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1932,9 +2024,12 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1971,32 +2066,35 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>871900</v>
+        <v>885500</v>
       </c>
       <c r="E45" s="3">
-        <v>819000</v>
+        <v>849800</v>
       </c>
       <c r="F45" s="3">
-        <v>286600</v>
+        <v>798200</v>
       </c>
       <c r="G45" s="3">
-        <v>18400</v>
+        <v>279300</v>
       </c>
       <c r="H45" s="3">
-        <v>19900</v>
+        <v>18000</v>
       </c>
       <c r="I45" s="3">
-        <v>13400</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+        <v>19400</v>
+      </c>
+      <c r="J45" s="3">
+        <v>13100</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -2010,9 +2108,12 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2049,32 +2150,35 @@
       <c r="N46" s="3">
         <v>0</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O46" s="3">
+        <v>0</v>
+      </c>
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>30418300</v>
+        <v>35943100</v>
       </c>
       <c r="E47" s="3">
-        <v>21699400</v>
+        <v>29647600</v>
       </c>
       <c r="F47" s="3">
-        <v>16225600</v>
+        <v>21149600</v>
       </c>
       <c r="G47" s="3">
-        <v>7678600</v>
+        <v>15814500</v>
       </c>
       <c r="H47" s="3">
-        <v>3016900</v>
+        <v>7484000</v>
       </c>
       <c r="I47" s="3">
-        <v>1113300</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+        <v>2940400</v>
+      </c>
+      <c r="J47" s="3">
+        <v>1085100</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -2088,32 +2192,35 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>117100</v>
+        <v>131300</v>
       </c>
       <c r="E48" s="3">
-        <v>123100</v>
+        <v>114100</v>
       </c>
       <c r="F48" s="3">
-        <v>79600</v>
+        <v>119900</v>
       </c>
       <c r="G48" s="3">
-        <v>76100</v>
+        <v>77600</v>
       </c>
       <c r="H48" s="3">
-        <v>20400</v>
+        <v>74100</v>
       </c>
       <c r="I48" s="3">
-        <v>9700</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+        <v>19900</v>
+      </c>
+      <c r="J48" s="3">
+        <v>9400</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -2127,32 +2234,35 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>173600</v>
+        <v>501500</v>
       </c>
       <c r="E49" s="3">
-        <v>168800</v>
+        <v>169200</v>
       </c>
       <c r="F49" s="3">
-        <v>146700</v>
+        <v>164500</v>
       </c>
       <c r="G49" s="3">
-        <v>113800</v>
+        <v>143000</v>
       </c>
       <c r="H49" s="3">
-        <v>103800</v>
+        <v>110900</v>
       </c>
       <c r="I49" s="3">
-        <v>99400</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+        <v>101200</v>
+      </c>
+      <c r="J49" s="3">
+        <v>96800</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2166,9 +2276,12 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2205,9 +2318,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2244,32 +2360,35 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>331500</v>
+        <v>421700</v>
       </c>
       <c r="E52" s="3">
-        <v>261800</v>
+        <v>323100</v>
       </c>
       <c r="F52" s="3">
-        <v>103900</v>
+        <v>255100</v>
       </c>
       <c r="G52" s="3">
-        <v>58500</v>
+        <v>101200</v>
       </c>
       <c r="H52" s="3">
-        <v>31300</v>
+        <v>57000</v>
       </c>
       <c r="I52" s="3">
-        <v>46600</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+        <v>30500</v>
+      </c>
+      <c r="J52" s="3">
+        <v>45400</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2283,9 +2402,12 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2322,32 +2444,35 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>39488100</v>
+        <v>49912800</v>
       </c>
       <c r="E54" s="3">
-        <v>28652600</v>
+        <v>38487600</v>
       </c>
       <c r="F54" s="3">
-        <v>19746500</v>
+        <v>27926600</v>
       </c>
       <c r="G54" s="3">
-        <v>8970100</v>
+        <v>19246200</v>
       </c>
       <c r="H54" s="3">
-        <v>3644600</v>
+        <v>8742900</v>
       </c>
       <c r="I54" s="3">
-        <v>1467400</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+        <v>3552300</v>
+      </c>
+      <c r="J54" s="3">
+        <v>1430200</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2361,9 +2486,12 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2379,8 +2507,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2396,31 +2525,32 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>127000</v>
+        <v>190000</v>
       </c>
       <c r="E57" s="3">
-        <v>178400</v>
+        <v>123700</v>
       </c>
       <c r="F57" s="3">
-        <v>176700</v>
+        <v>173900</v>
       </c>
       <c r="G57" s="3">
-        <v>54900</v>
+        <v>172300</v>
       </c>
       <c r="H57" s="3">
-        <v>27700</v>
+        <v>53500</v>
       </c>
       <c r="I57" s="3">
-        <v>14700</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+        <v>27000</v>
+      </c>
+      <c r="J57" s="3">
+        <v>14300</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2434,32 +2564,35 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>10134200</v>
+        <v>10775400</v>
       </c>
       <c r="E58" s="3">
-        <v>6328600</v>
+        <v>9877400</v>
       </c>
       <c r="F58" s="3">
-        <v>7056300</v>
+        <v>6168300</v>
       </c>
       <c r="G58" s="3">
-        <v>3731800</v>
+        <v>6877500</v>
       </c>
       <c r="H58" s="3">
-        <v>1648100</v>
+        <v>3637200</v>
       </c>
       <c r="I58" s="3">
-        <v>279000</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>1606300</v>
+      </c>
+      <c r="J58" s="3">
+        <v>272000</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2473,32 +2606,35 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>274200</v>
+        <v>341900</v>
       </c>
       <c r="E59" s="3">
-        <v>323200</v>
+        <v>267300</v>
       </c>
       <c r="F59" s="3">
-        <v>226900</v>
+        <v>315000</v>
       </c>
       <c r="G59" s="3">
-        <v>172300</v>
+        <v>221100</v>
       </c>
       <c r="H59" s="3">
-        <v>73000</v>
+        <v>168000</v>
       </c>
       <c r="I59" s="3">
-        <v>73300</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>71100</v>
+      </c>
+      <c r="J59" s="3">
+        <v>71400</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2512,9 +2648,12 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2551,32 +2690,35 @@
       <c r="N60" s="3">
         <v>0</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O60" s="3">
+        <v>0</v>
+      </c>
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>776700</v>
+        <v>440700</v>
       </c>
       <c r="E61" s="3">
-        <v>943600</v>
+        <v>757000</v>
       </c>
       <c r="F61" s="3">
-        <v>121100</v>
+        <v>919700</v>
       </c>
       <c r="G61" s="3">
-        <v>202500</v>
+        <v>118100</v>
       </c>
       <c r="H61" s="3">
-        <v>156600</v>
+        <v>197400</v>
       </c>
       <c r="I61" s="3">
-        <v>151500</v>
+        <v>152700</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>147600</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2590,32 +2732,35 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>9436000</v>
+        <v>11342400</v>
       </c>
       <c r="E62" s="3">
-        <v>6576000</v>
+        <v>9197000</v>
       </c>
       <c r="F62" s="3">
-        <v>2758700</v>
+        <v>6409400</v>
       </c>
       <c r="G62" s="3">
-        <v>777200</v>
+        <v>2688800</v>
       </c>
       <c r="H62" s="3">
-        <v>6100</v>
+        <v>757500</v>
       </c>
       <c r="I62" s="3">
-        <v>3800</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+        <v>5900</v>
+      </c>
+      <c r="J62" s="3">
+        <v>3700</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2629,9 +2774,12 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2668,9 +2816,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2707,9 +2858,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2746,32 +2900,35 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>35985000</v>
+        <v>46014600</v>
       </c>
       <c r="E66" s="3">
-        <v>25688000</v>
+        <v>35073300</v>
       </c>
       <c r="F66" s="3">
-        <v>17506200</v>
+        <v>25037200</v>
       </c>
       <c r="G66" s="3">
-        <v>7499200</v>
+        <v>17062700</v>
       </c>
       <c r="H66" s="3">
-        <v>3215900</v>
+        <v>7309200</v>
       </c>
       <c r="I66" s="3">
-        <v>1232200</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+        <v>3134500</v>
+      </c>
+      <c r="J66" s="3">
+        <v>1201000</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2785,9 +2942,12 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2803,8 +2963,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2841,9 +3002,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2880,9 +3044,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2919,9 +3086,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2958,32 +3128,35 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>3939100</v>
+        <v>3846100</v>
       </c>
       <c r="E72" s="3">
-        <v>3068700</v>
+        <v>3839300</v>
       </c>
       <c r="F72" s="3">
-        <v>2192800</v>
+        <v>2990900</v>
       </c>
       <c r="G72" s="3">
-        <v>1427800</v>
+        <v>2137300</v>
       </c>
       <c r="H72" s="3">
-        <v>194900</v>
+        <v>1391600</v>
       </c>
       <c r="I72" s="3">
-        <v>141000</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+        <v>189900</v>
+      </c>
+      <c r="J72" s="3">
+        <v>137400</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2997,9 +3170,12 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3036,9 +3212,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3075,9 +3254,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3114,32 +3296,35 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3503100</v>
+        <v>3898200</v>
       </c>
       <c r="E76" s="3">
-        <v>2964500</v>
+        <v>3414300</v>
       </c>
       <c r="F76" s="3">
-        <v>2240300</v>
+        <v>2889400</v>
       </c>
       <c r="G76" s="3">
-        <v>1471000</v>
+        <v>2183500</v>
       </c>
       <c r="H76" s="3">
-        <v>428700</v>
+        <v>1433700</v>
       </c>
       <c r="I76" s="3">
-        <v>235200</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+        <v>417800</v>
+      </c>
+      <c r="J76" s="3">
+        <v>229200</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -3153,9 +3338,12 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3192,41 +3380,44 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3236,36 +3427,39 @@
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>736000</v>
+        <v>781400</v>
       </c>
       <c r="E81" s="3">
-        <v>738100</v>
+        <v>717300</v>
       </c>
       <c r="F81" s="3">
-        <v>427000</v>
+        <v>719400</v>
       </c>
       <c r="G81" s="3">
-        <v>222200</v>
+        <v>416200</v>
       </c>
       <c r="H81" s="3">
-        <v>94900</v>
+        <v>216600</v>
       </c>
       <c r="I81" s="3">
-        <v>85100</v>
+        <v>92500</v>
       </c>
       <c r="J81" s="3">
+        <v>82900</v>
+      </c>
+      <c r="K81" s="3">
         <v>38800</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3275,9 +3469,12 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3293,35 +3490,36 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>42300</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E83" s="3">
-        <v>47700</v>
+        <v>41300</v>
       </c>
       <c r="F83" s="3">
-        <v>29500</v>
+        <v>46400</v>
       </c>
       <c r="G83" s="3">
-        <v>18700</v>
+        <v>28700</v>
       </c>
       <c r="H83" s="3">
-        <v>10900</v>
+        <v>18200</v>
       </c>
       <c r="I83" s="3">
-        <v>5600</v>
+        <v>10600</v>
       </c>
       <c r="J83" s="3">
+        <v>5500</v>
+      </c>
+      <c r="K83" s="3">
         <v>4700</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3331,9 +3529,12 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3370,9 +3571,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3409,9 +3613,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3448,9 +3655,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3487,9 +3697,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3526,36 +3739,39 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>370900</v>
+      <c r="D89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E89" s="3">
-        <v>-826700</v>
+        <v>361500</v>
       </c>
       <c r="F89" s="3">
-        <v>310700</v>
+        <v>-805800</v>
       </c>
       <c r="G89" s="3">
-        <v>-784300</v>
+        <v>302800</v>
       </c>
       <c r="H89" s="3">
-        <v>-93900</v>
+        <v>-764400</v>
       </c>
       <c r="I89" s="3">
-        <v>54000</v>
+        <v>-91500</v>
       </c>
       <c r="J89" s="3">
+        <v>52600</v>
+      </c>
+      <c r="K89" s="3">
         <v>1000</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3565,9 +3781,12 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3583,35 +3802,36 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-9200</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E91" s="3">
-        <v>-27900</v>
+        <v>-8900</v>
       </c>
       <c r="F91" s="3">
-        <v>-29900</v>
+        <v>-27100</v>
       </c>
       <c r="G91" s="3">
-        <v>-14900</v>
+        <v>-29100</v>
       </c>
       <c r="H91" s="3">
-        <v>-11000</v>
+        <v>-14500</v>
       </c>
       <c r="I91" s="3">
-        <v>-4200</v>
+        <v>-10700</v>
       </c>
       <c r="J91" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="K91" s="3">
         <v>-2600</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3621,9 +3841,12 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3660,9 +3883,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3699,36 +3925,39 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-76300</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E94" s="3">
-        <v>-236600</v>
+        <v>-74400</v>
       </c>
       <c r="F94" s="3">
-        <v>-119700</v>
+        <v>-230600</v>
       </c>
       <c r="G94" s="3">
-        <v>-33200</v>
+        <v>-116600</v>
       </c>
       <c r="H94" s="3">
-        <v>-30200</v>
+        <v>-32400</v>
       </c>
       <c r="I94" s="3">
-        <v>-93700</v>
+        <v>-29500</v>
       </c>
       <c r="J94" s="3">
+        <v>-91300</v>
+      </c>
+      <c r="K94" s="3">
         <v>-6500</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3738,9 +3967,12 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3756,8 +3988,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3771,20 +4004,20 @@
         <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-102800</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-66800</v>
+        <v>-100200</v>
       </c>
       <c r="I96" s="3">
-        <v>-39100</v>
+        <v>-65100</v>
       </c>
       <c r="J96" s="3">
+        <v>-38100</v>
+      </c>
+      <c r="K96" s="3">
         <v>-35900</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -3794,9 +4027,12 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3833,9 +4069,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3872,9 +4111,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3911,36 +4153,39 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>-41200</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E100" s="3">
-        <v>1365200</v>
+        <v>-40100</v>
       </c>
       <c r="F100" s="3">
-        <v>162200</v>
+        <v>1330600</v>
       </c>
       <c r="G100" s="3">
-        <v>870600</v>
+        <v>158100</v>
       </c>
       <c r="H100" s="3">
-        <v>78200</v>
+        <v>848500</v>
       </c>
       <c r="I100" s="3">
-        <v>120200</v>
+        <v>76200</v>
       </c>
       <c r="J100" s="3">
+        <v>117100</v>
+      </c>
+      <c r="K100" s="3">
         <v>16900</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3950,36 +4195,39 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>-3400</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E101" s="3">
-        <v>-77500</v>
+        <v>-3300</v>
       </c>
       <c r="F101" s="3">
-        <v>11300</v>
+        <v>-75500</v>
       </c>
       <c r="G101" s="3">
+        <v>11100</v>
+      </c>
+      <c r="H101" s="3">
         <v>500</v>
       </c>
-      <c r="H101" s="3">
-        <v>3100</v>
-      </c>
       <c r="I101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J101" s="3">
         <v>800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1500</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3989,36 +4237,39 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>250000</v>
+      <c r="D102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E102" s="3">
-        <v>224400</v>
+        <v>243600</v>
       </c>
       <c r="F102" s="3">
-        <v>364500</v>
+        <v>218800</v>
       </c>
       <c r="G102" s="3">
-        <v>53700</v>
+        <v>355300</v>
       </c>
       <c r="H102" s="3">
-        <v>-42900</v>
+        <v>52300</v>
       </c>
       <c r="I102" s="3">
-        <v>81300</v>
+        <v>-41800</v>
       </c>
       <c r="J102" s="3">
+        <v>79200</v>
+      </c>
+      <c r="K102" s="3">
         <v>9900</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4028,7 +4279,10 @@
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/XP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/XP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
   <si>
     <t>XP</t>
   </si>
@@ -724,25 +724,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>2978400</v>
+        <v>2745600</v>
       </c>
       <c r="E8" s="3">
-        <v>2675100</v>
+        <v>2466100</v>
       </c>
       <c r="F8" s="3">
-        <v>2420500</v>
+        <v>2231400</v>
       </c>
       <c r="G8" s="3">
-        <v>1633700</v>
+        <v>1506100</v>
       </c>
       <c r="H8" s="3">
-        <v>1027700</v>
+        <v>947400</v>
       </c>
       <c r="I8" s="3">
-        <v>592900</v>
+        <v>546600</v>
       </c>
       <c r="J8" s="3">
-        <v>382100</v>
+        <v>352300</v>
       </c>
       <c r="K8" s="3">
         <v>257400</v>
@@ -951,17 +951,17 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>14400</v>
       </c>
       <c r="E14" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="F14" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="G14" s="3">
-        <v>10400</v>
+        <v>9600</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -993,26 +993,26 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>3</v>
+      <c r="D15" s="3">
+        <v>46600</v>
       </c>
       <c r="E15" s="3">
-        <v>41300</v>
+        <v>38000</v>
       </c>
       <c r="F15" s="3">
-        <v>46400</v>
+        <v>42800</v>
       </c>
       <c r="G15" s="3">
-        <v>28700</v>
+        <v>26500</v>
       </c>
       <c r="H15" s="3">
-        <v>18300</v>
+        <v>16800</v>
       </c>
       <c r="I15" s="3">
-        <v>10600</v>
+        <v>9800</v>
       </c>
       <c r="J15" s="3">
-        <v>5500</v>
+        <v>5100</v>
       </c>
       <c r="K15" s="3">
         <v>4700</v>
@@ -1051,25 +1051,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2080400</v>
+        <v>1917800</v>
       </c>
       <c r="E17" s="3">
-        <v>1901600</v>
+        <v>1753100</v>
       </c>
       <c r="F17" s="3">
-        <v>1627100</v>
+        <v>1500000</v>
       </c>
       <c r="G17" s="3">
-        <v>1138100</v>
+        <v>1049100</v>
       </c>
       <c r="H17" s="3">
-        <v>701300</v>
+        <v>646500</v>
       </c>
       <c r="I17" s="3">
-        <v>450000</v>
+        <v>414900</v>
       </c>
       <c r="J17" s="3">
-        <v>254500</v>
+        <v>234700</v>
       </c>
       <c r="K17" s="3">
         <v>180500</v>
@@ -1093,25 +1093,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>898100</v>
+        <v>827800</v>
       </c>
       <c r="E18" s="3">
-        <v>773400</v>
+        <v>713000</v>
       </c>
       <c r="F18" s="3">
-        <v>793400</v>
+        <v>731400</v>
       </c>
       <c r="G18" s="3">
-        <v>495700</v>
+        <v>457000</v>
       </c>
       <c r="H18" s="3">
-        <v>326400</v>
+        <v>300900</v>
       </c>
       <c r="I18" s="3">
-        <v>142900</v>
+        <v>131700</v>
       </c>
       <c r="J18" s="3">
-        <v>127600</v>
+        <v>117600</v>
       </c>
       <c r="K18" s="3">
         <v>76900</v>
@@ -1153,13 +1153,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>14400</v>
+        <v>13600</v>
       </c>
       <c r="E20" s="3">
-        <v>-2400</v>
+        <v>-2200</v>
       </c>
       <c r="F20" s="3">
-        <v>-1500</v>
+        <v>-1400</v>
       </c>
       <c r="G20" s="3">
         <v>200</v>
@@ -1168,10 +1168,10 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>-14500</v>
+        <v>-13400</v>
       </c>
       <c r="J20" s="3">
-        <v>-12200</v>
+        <v>-11300</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1194,26 +1194,26 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>888400</v>
       </c>
       <c r="E21" s="3">
-        <v>812400</v>
+        <v>749100</v>
       </c>
       <c r="F21" s="3">
-        <v>838500</v>
+        <v>773200</v>
       </c>
       <c r="G21" s="3">
-        <v>524700</v>
+        <v>483800</v>
       </c>
       <c r="H21" s="3">
-        <v>344600</v>
+        <v>317800</v>
       </c>
       <c r="I21" s="3">
-        <v>139000</v>
+        <v>128200</v>
       </c>
       <c r="J21" s="3">
-        <v>120900</v>
+        <v>111400</v>
       </c>
       <c r="K21" s="3">
         <v>81600</v>
@@ -1237,19 +1237,19 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>123700</v>
+        <v>114100</v>
       </c>
       <c r="E22" s="3">
-        <v>80600</v>
+        <v>74300</v>
       </c>
       <c r="F22" s="3">
-        <v>27200</v>
+        <v>25100</v>
       </c>
       <c r="G22" s="3">
-        <v>10600</v>
+        <v>9700</v>
       </c>
       <c r="H22" s="3">
-        <v>16900</v>
+        <v>15600</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
@@ -1279,25 +1279,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>788900</v>
+        <v>727300</v>
       </c>
       <c r="E23" s="3">
-        <v>690400</v>
+        <v>636400</v>
       </c>
       <c r="F23" s="3">
-        <v>764600</v>
+        <v>704900</v>
       </c>
       <c r="G23" s="3">
-        <v>485300</v>
+        <v>447400</v>
       </c>
       <c r="H23" s="3">
-        <v>309500</v>
+        <v>285300</v>
       </c>
       <c r="I23" s="3">
-        <v>128400</v>
+        <v>118400</v>
       </c>
       <c r="J23" s="3">
-        <v>115300</v>
+        <v>106300</v>
       </c>
       <c r="K23" s="3">
         <v>76900</v>
@@ -1321,25 +1321,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>7400</v>
+        <v>6800</v>
       </c>
       <c r="E24" s="3">
-        <v>-27200</v>
+        <v>-25000</v>
       </c>
       <c r="F24" s="3">
-        <v>44600</v>
+        <v>41100</v>
       </c>
       <c r="G24" s="3">
-        <v>68100</v>
+        <v>62800</v>
       </c>
       <c r="H24" s="3">
-        <v>91100</v>
+        <v>84000</v>
       </c>
       <c r="I24" s="3">
-        <v>35200</v>
+        <v>32400</v>
       </c>
       <c r="J24" s="3">
-        <v>30500</v>
+        <v>28100</v>
       </c>
       <c r="K24" s="3">
         <v>26800</v>
@@ -1405,25 +1405,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>781400</v>
+        <v>720500</v>
       </c>
       <c r="E26" s="3">
-        <v>717500</v>
+        <v>661500</v>
       </c>
       <c r="F26" s="3">
-        <v>720000</v>
+        <v>663700</v>
       </c>
       <c r="G26" s="3">
-        <v>417200</v>
+        <v>384600</v>
       </c>
       <c r="H26" s="3">
-        <v>218400</v>
+        <v>201300</v>
       </c>
       <c r="I26" s="3">
-        <v>93300</v>
+        <v>86000</v>
       </c>
       <c r="J26" s="3">
-        <v>84900</v>
+        <v>78300</v>
       </c>
       <c r="K26" s="3">
         <v>50100</v>
@@ -1447,25 +1447,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>781400</v>
+        <v>720300</v>
       </c>
       <c r="E27" s="3">
-        <v>717300</v>
+        <v>661300</v>
       </c>
       <c r="F27" s="3">
-        <v>719400</v>
+        <v>663200</v>
       </c>
       <c r="G27" s="3">
-        <v>416200</v>
+        <v>383600</v>
       </c>
       <c r="H27" s="3">
-        <v>216600</v>
+        <v>199600</v>
       </c>
       <c r="I27" s="3">
-        <v>92500</v>
+        <v>85300</v>
       </c>
       <c r="J27" s="3">
-        <v>82900</v>
+        <v>76500</v>
       </c>
       <c r="K27" s="3">
         <v>38800</v>
@@ -1657,13 +1657,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-14400</v>
+        <v>-13600</v>
       </c>
       <c r="E32" s="3">
-        <v>2400</v>
+        <v>2200</v>
       </c>
       <c r="F32" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="G32" s="3">
         <v>-200</v>
@@ -1672,10 +1672,10 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>14500</v>
+        <v>13400</v>
       </c>
       <c r="J32" s="3">
-        <v>12200</v>
+        <v>11300</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -1699,25 +1699,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>781400</v>
+        <v>720300</v>
       </c>
       <c r="E33" s="3">
-        <v>717300</v>
+        <v>661300</v>
       </c>
       <c r="F33" s="3">
-        <v>719400</v>
+        <v>663200</v>
       </c>
       <c r="G33" s="3">
-        <v>416200</v>
+        <v>383600</v>
       </c>
       <c r="H33" s="3">
-        <v>216600</v>
+        <v>199600</v>
       </c>
       <c r="I33" s="3">
-        <v>92500</v>
+        <v>85300</v>
       </c>
       <c r="J33" s="3">
-        <v>82900</v>
+        <v>76500</v>
       </c>
       <c r="K33" s="3">
         <v>38800</v>
@@ -1783,25 +1783,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>781400</v>
+        <v>720300</v>
       </c>
       <c r="E35" s="3">
-        <v>717300</v>
+        <v>661300</v>
       </c>
       <c r="F35" s="3">
-        <v>719400</v>
+        <v>663200</v>
       </c>
       <c r="G35" s="3">
-        <v>416200</v>
+        <v>383600</v>
       </c>
       <c r="H35" s="3">
-        <v>216600</v>
+        <v>199600</v>
       </c>
       <c r="I35" s="3">
-        <v>92500</v>
+        <v>85300</v>
       </c>
       <c r="J35" s="3">
-        <v>82900</v>
+        <v>76500</v>
       </c>
       <c r="K35" s="3">
         <v>38800</v>
@@ -1908,25 +1908,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>790300</v>
+        <v>728600</v>
       </c>
       <c r="E41" s="3">
-        <v>712100</v>
+        <v>656500</v>
       </c>
       <c r="F41" s="3">
-        <v>498200</v>
+        <v>459200</v>
       </c>
       <c r="G41" s="3">
-        <v>391800</v>
+        <v>361200</v>
       </c>
       <c r="H41" s="3">
-        <v>22000</v>
+        <v>20300</v>
       </c>
       <c r="I41" s="3">
-        <v>13700</v>
+        <v>12600</v>
       </c>
       <c r="J41" s="3">
-        <v>30700</v>
+        <v>28300</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1992,25 +1992,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>185600</v>
+        <v>171200</v>
       </c>
       <c r="E43" s="3">
-        <v>152500</v>
+        <v>140600</v>
       </c>
       <c r="F43" s="3">
-        <v>124700</v>
+        <v>115000</v>
       </c>
       <c r="G43" s="3">
-        <v>127100</v>
+        <v>117100</v>
       </c>
       <c r="H43" s="3">
-        <v>141400</v>
+        <v>130300</v>
       </c>
       <c r="I43" s="3">
-        <v>80700</v>
+        <v>74400</v>
       </c>
       <c r="J43" s="3">
-        <v>34400</v>
+        <v>31800</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -2076,25 +2076,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>885500</v>
+        <v>816300</v>
       </c>
       <c r="E45" s="3">
-        <v>849800</v>
+        <v>783400</v>
       </c>
       <c r="F45" s="3">
-        <v>798200</v>
+        <v>735900</v>
       </c>
       <c r="G45" s="3">
-        <v>279300</v>
+        <v>257500</v>
       </c>
       <c r="H45" s="3">
-        <v>18000</v>
+        <v>16600</v>
       </c>
       <c r="I45" s="3">
-        <v>19400</v>
+        <v>17900</v>
       </c>
       <c r="J45" s="3">
-        <v>13100</v>
+        <v>12100</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -2160,25 +2160,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>35943100</v>
+        <v>33134700</v>
       </c>
       <c r="E47" s="3">
-        <v>29647600</v>
+        <v>27331100</v>
       </c>
       <c r="F47" s="3">
-        <v>21149600</v>
+        <v>19497000</v>
       </c>
       <c r="G47" s="3">
-        <v>15814500</v>
+        <v>14578800</v>
       </c>
       <c r="H47" s="3">
-        <v>7484000</v>
+        <v>6899300</v>
       </c>
       <c r="I47" s="3">
-        <v>2940400</v>
+        <v>2710700</v>
       </c>
       <c r="J47" s="3">
-        <v>1085100</v>
+        <v>1000300</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -2202,25 +2202,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>131300</v>
+        <v>121000</v>
       </c>
       <c r="E48" s="3">
-        <v>114100</v>
+        <v>105200</v>
       </c>
       <c r="F48" s="3">
-        <v>119900</v>
+        <v>110600</v>
       </c>
       <c r="G48" s="3">
-        <v>77600</v>
+        <v>71500</v>
       </c>
       <c r="H48" s="3">
-        <v>74100</v>
+        <v>68400</v>
       </c>
       <c r="I48" s="3">
-        <v>19900</v>
+        <v>18300</v>
       </c>
       <c r="J48" s="3">
-        <v>9400</v>
+        <v>8700</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -2244,25 +2244,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>501500</v>
+        <v>462300</v>
       </c>
       <c r="E49" s="3">
-        <v>169200</v>
+        <v>156000</v>
       </c>
       <c r="F49" s="3">
-        <v>164500</v>
+        <v>151700</v>
       </c>
       <c r="G49" s="3">
-        <v>143000</v>
+        <v>131800</v>
       </c>
       <c r="H49" s="3">
-        <v>110900</v>
+        <v>102300</v>
       </c>
       <c r="I49" s="3">
-        <v>101200</v>
+        <v>93300</v>
       </c>
       <c r="J49" s="3">
-        <v>96800</v>
+        <v>89300</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2370,25 +2370,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>421700</v>
+        <v>388800</v>
       </c>
       <c r="E52" s="3">
-        <v>323100</v>
+        <v>297800</v>
       </c>
       <c r="F52" s="3">
-        <v>255100</v>
+        <v>235200</v>
       </c>
       <c r="G52" s="3">
-        <v>101200</v>
+        <v>93300</v>
       </c>
       <c r="H52" s="3">
-        <v>57000</v>
+        <v>52600</v>
       </c>
       <c r="I52" s="3">
-        <v>30500</v>
+        <v>28200</v>
       </c>
       <c r="J52" s="3">
-        <v>45400</v>
+        <v>41800</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2454,25 +2454,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>49912800</v>
+        <v>46012800</v>
       </c>
       <c r="E54" s="3">
-        <v>38487600</v>
+        <v>35480300</v>
       </c>
       <c r="F54" s="3">
-        <v>27926600</v>
+        <v>25744500</v>
       </c>
       <c r="G54" s="3">
-        <v>19246200</v>
+        <v>17742300</v>
       </c>
       <c r="H54" s="3">
-        <v>8742900</v>
+        <v>8059700</v>
       </c>
       <c r="I54" s="3">
-        <v>3552300</v>
+        <v>3274700</v>
       </c>
       <c r="J54" s="3">
-        <v>1430200</v>
+        <v>1318500</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2532,25 +2532,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>190000</v>
+        <v>175200</v>
       </c>
       <c r="E57" s="3">
-        <v>123700</v>
+        <v>114100</v>
       </c>
       <c r="F57" s="3">
-        <v>173900</v>
+        <v>160300</v>
       </c>
       <c r="G57" s="3">
-        <v>172300</v>
+        <v>158800</v>
       </c>
       <c r="H57" s="3">
-        <v>53500</v>
+        <v>49300</v>
       </c>
       <c r="I57" s="3">
-        <v>27000</v>
+        <v>24900</v>
       </c>
       <c r="J57" s="3">
-        <v>14300</v>
+        <v>13200</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2574,25 +2574,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>10775400</v>
+        <v>10771400</v>
       </c>
       <c r="E58" s="3">
-        <v>9877400</v>
+        <v>9105600</v>
       </c>
       <c r="F58" s="3">
-        <v>6168300</v>
+        <v>5686300</v>
       </c>
       <c r="G58" s="3">
-        <v>6877500</v>
+        <v>6340100</v>
       </c>
       <c r="H58" s="3">
-        <v>3637200</v>
+        <v>3353000</v>
       </c>
       <c r="I58" s="3">
-        <v>1606300</v>
+        <v>1480800</v>
       </c>
       <c r="J58" s="3">
-        <v>272000</v>
+        <v>250700</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2616,25 +2616,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>341900</v>
+        <v>315200</v>
       </c>
       <c r="E59" s="3">
-        <v>267300</v>
+        <v>246400</v>
       </c>
       <c r="F59" s="3">
-        <v>315000</v>
+        <v>290400</v>
       </c>
       <c r="G59" s="3">
-        <v>221100</v>
+        <v>203800</v>
       </c>
       <c r="H59" s="3">
-        <v>168000</v>
+        <v>154800</v>
       </c>
       <c r="I59" s="3">
-        <v>71100</v>
+        <v>65600</v>
       </c>
       <c r="J59" s="3">
-        <v>71400</v>
+        <v>65800</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2700,25 +2700,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>440700</v>
+        <v>647100</v>
       </c>
       <c r="E61" s="3">
-        <v>757000</v>
+        <v>697900</v>
       </c>
       <c r="F61" s="3">
-        <v>919700</v>
+        <v>847800</v>
       </c>
       <c r="G61" s="3">
-        <v>118100</v>
+        <v>108800</v>
       </c>
       <c r="H61" s="3">
-        <v>197400</v>
+        <v>181900</v>
       </c>
       <c r="I61" s="3">
-        <v>152700</v>
+        <v>140700</v>
       </c>
       <c r="J61" s="3">
-        <v>147600</v>
+        <v>136100</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2742,25 +2742,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>11342400</v>
+        <v>10456100</v>
       </c>
       <c r="E62" s="3">
-        <v>9197000</v>
+        <v>8478300</v>
       </c>
       <c r="F62" s="3">
-        <v>6409400</v>
+        <v>5908600</v>
       </c>
       <c r="G62" s="3">
-        <v>2688800</v>
+        <v>2478700</v>
       </c>
       <c r="H62" s="3">
-        <v>757500</v>
+        <v>698300</v>
       </c>
       <c r="I62" s="3">
-        <v>5900</v>
+        <v>5500</v>
       </c>
       <c r="J62" s="3">
-        <v>3700</v>
+        <v>3400</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2910,25 +2910,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>46014600</v>
+        <v>42419300</v>
       </c>
       <c r="E66" s="3">
-        <v>35073300</v>
+        <v>32332800</v>
       </c>
       <c r="F66" s="3">
-        <v>25037200</v>
+        <v>23080900</v>
       </c>
       <c r="G66" s="3">
-        <v>17062700</v>
+        <v>15729500</v>
       </c>
       <c r="H66" s="3">
-        <v>7309200</v>
+        <v>6738100</v>
       </c>
       <c r="I66" s="3">
-        <v>3134500</v>
+        <v>2889600</v>
       </c>
       <c r="J66" s="3">
-        <v>1201000</v>
+        <v>1107100</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -3138,25 +3138,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>3846100</v>
+        <v>3545500</v>
       </c>
       <c r="E72" s="3">
-        <v>3839300</v>
+        <v>3539300</v>
       </c>
       <c r="F72" s="3">
-        <v>2990900</v>
+        <v>2757200</v>
       </c>
       <c r="G72" s="3">
-        <v>2137300</v>
+        <v>1970300</v>
       </c>
       <c r="H72" s="3">
-        <v>1391600</v>
+        <v>1282900</v>
       </c>
       <c r="I72" s="3">
-        <v>189900</v>
+        <v>175100</v>
       </c>
       <c r="J72" s="3">
-        <v>137400</v>
+        <v>126700</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -3306,25 +3306,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3898200</v>
+        <v>3593500</v>
       </c>
       <c r="E76" s="3">
-        <v>3414300</v>
+        <v>3147500</v>
       </c>
       <c r="F76" s="3">
-        <v>2889400</v>
+        <v>2663700</v>
       </c>
       <c r="G76" s="3">
-        <v>2183500</v>
+        <v>2012900</v>
       </c>
       <c r="H76" s="3">
-        <v>1433700</v>
+        <v>1321700</v>
       </c>
       <c r="I76" s="3">
-        <v>417800</v>
+        <v>385200</v>
       </c>
       <c r="J76" s="3">
-        <v>229200</v>
+        <v>211300</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -3437,25 +3437,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>781400</v>
+        <v>720300</v>
       </c>
       <c r="E81" s="3">
-        <v>717300</v>
+        <v>661300</v>
       </c>
       <c r="F81" s="3">
-        <v>719400</v>
+        <v>663200</v>
       </c>
       <c r="G81" s="3">
-        <v>416200</v>
+        <v>383600</v>
       </c>
       <c r="H81" s="3">
-        <v>216600</v>
+        <v>199600</v>
       </c>
       <c r="I81" s="3">
-        <v>92500</v>
+        <v>85300</v>
       </c>
       <c r="J81" s="3">
-        <v>82900</v>
+        <v>76500</v>
       </c>
       <c r="K81" s="3">
         <v>38800</v>
@@ -3496,26 +3496,26 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>46600</v>
       </c>
       <c r="E83" s="3">
-        <v>41300</v>
+        <v>38000</v>
       </c>
       <c r="F83" s="3">
-        <v>46400</v>
+        <v>42800</v>
       </c>
       <c r="G83" s="3">
-        <v>28700</v>
+        <v>26500</v>
       </c>
       <c r="H83" s="3">
-        <v>18200</v>
+        <v>16800</v>
       </c>
       <c r="I83" s="3">
-        <v>10600</v>
+        <v>9800</v>
       </c>
       <c r="J83" s="3">
-        <v>5500</v>
+        <v>5100</v>
       </c>
       <c r="K83" s="3">
         <v>4700</v>
@@ -3748,26 +3748,26 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>1501600</v>
       </c>
       <c r="E89" s="3">
-        <v>361500</v>
+        <v>333300</v>
       </c>
       <c r="F89" s="3">
-        <v>-805800</v>
+        <v>-742800</v>
       </c>
       <c r="G89" s="3">
-        <v>302800</v>
+        <v>279100</v>
       </c>
       <c r="H89" s="3">
-        <v>-764400</v>
+        <v>-704700</v>
       </c>
       <c r="I89" s="3">
-        <v>-91500</v>
+        <v>-84400</v>
       </c>
       <c r="J89" s="3">
-        <v>52600</v>
+        <v>48500</v>
       </c>
       <c r="K89" s="3">
         <v>1000</v>
@@ -3808,26 +3808,26 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>-12200</v>
       </c>
       <c r="E91" s="3">
-        <v>-8900</v>
+        <v>-8200</v>
       </c>
       <c r="F91" s="3">
-        <v>-27100</v>
+        <v>-25000</v>
       </c>
       <c r="G91" s="3">
-        <v>-29100</v>
+        <v>-26800</v>
       </c>
       <c r="H91" s="3">
-        <v>-14500</v>
+        <v>-13400</v>
       </c>
       <c r="I91" s="3">
-        <v>-10700</v>
+        <v>-9900</v>
       </c>
       <c r="J91" s="3">
-        <v>-4100</v>
+        <v>-3800</v>
       </c>
       <c r="K91" s="3">
         <v>-2600</v>
@@ -3934,26 +3934,26 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>99600</v>
       </c>
       <c r="E94" s="3">
-        <v>-74400</v>
+        <v>-68600</v>
       </c>
       <c r="F94" s="3">
-        <v>-230600</v>
+        <v>-212600</v>
       </c>
       <c r="G94" s="3">
-        <v>-116600</v>
+        <v>-107500</v>
       </c>
       <c r="H94" s="3">
-        <v>-32400</v>
+        <v>-29800</v>
       </c>
       <c r="I94" s="3">
-        <v>-29500</v>
+        <v>-27200</v>
       </c>
       <c r="J94" s="3">
-        <v>-91300</v>
+        <v>-84200</v>
       </c>
       <c r="K94" s="3">
         <v>-6500</v>
@@ -3995,7 +3995,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-654500</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -4007,13 +4007,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-100200</v>
+        <v>-92400</v>
       </c>
       <c r="I96" s="3">
-        <v>-65100</v>
+        <v>-60000</v>
       </c>
       <c r="J96" s="3">
-        <v>-38100</v>
+        <v>-35100</v>
       </c>
       <c r="K96" s="3">
         <v>-35900</v>
@@ -4162,26 +4162,26 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>-812000</v>
       </c>
       <c r="E100" s="3">
-        <v>-40100</v>
+        <v>-37000</v>
       </c>
       <c r="F100" s="3">
-        <v>1330600</v>
+        <v>1226700</v>
       </c>
       <c r="G100" s="3">
-        <v>158100</v>
+        <v>145700</v>
       </c>
       <c r="H100" s="3">
-        <v>848500</v>
+        <v>782200</v>
       </c>
       <c r="I100" s="3">
-        <v>76200</v>
+        <v>70200</v>
       </c>
       <c r="J100" s="3">
-        <v>117100</v>
+        <v>108000</v>
       </c>
       <c r="K100" s="3">
         <v>16900</v>
@@ -4204,23 +4204,23 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>-5200</v>
       </c>
       <c r="E101" s="3">
-        <v>-3300</v>
+        <v>-3100</v>
       </c>
       <c r="F101" s="3">
-        <v>-75500</v>
+        <v>-69600</v>
       </c>
       <c r="G101" s="3">
-        <v>11100</v>
+        <v>10200</v>
       </c>
       <c r="H101" s="3">
         <v>500</v>
       </c>
       <c r="I101" s="3">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="J101" s="3">
         <v>800</v>
@@ -4246,26 +4246,26 @@
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
+      <c r="D102" s="3">
+        <v>783900</v>
       </c>
       <c r="E102" s="3">
-        <v>243600</v>
+        <v>224600</v>
       </c>
       <c r="F102" s="3">
-        <v>218800</v>
+        <v>201700</v>
       </c>
       <c r="G102" s="3">
-        <v>355300</v>
+        <v>327500</v>
       </c>
       <c r="H102" s="3">
-        <v>52300</v>
+        <v>48200</v>
       </c>
       <c r="I102" s="3">
-        <v>-41800</v>
+        <v>-38500</v>
       </c>
       <c r="J102" s="3">
-        <v>79200</v>
+        <v>73000</v>
       </c>
       <c r="K102" s="3">
         <v>9900</v>

--- a/AAII_Financials/Yearly/XP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/XP_YR_FIN.xlsx
@@ -724,25 +724,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>2745600</v>
+        <v>2670800</v>
       </c>
       <c r="E8" s="3">
-        <v>2466100</v>
+        <v>2398900</v>
       </c>
       <c r="F8" s="3">
-        <v>2231400</v>
+        <v>2170600</v>
       </c>
       <c r="G8" s="3">
-        <v>1506100</v>
+        <v>1465100</v>
       </c>
       <c r="H8" s="3">
-        <v>947400</v>
+        <v>921600</v>
       </c>
       <c r="I8" s="3">
-        <v>546600</v>
+        <v>531700</v>
       </c>
       <c r="J8" s="3">
-        <v>352300</v>
+        <v>342700</v>
       </c>
       <c r="K8" s="3">
         <v>257400</v>
@@ -952,16 +952,16 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>14400</v>
+        <v>14000</v>
       </c>
       <c r="E14" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="F14" s="3">
         <v>800</v>
       </c>
       <c r="G14" s="3">
-        <v>9600</v>
+        <v>9400</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -994,25 +994,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>46600</v>
+        <v>45400</v>
       </c>
       <c r="E15" s="3">
-        <v>38000</v>
+        <v>37000</v>
       </c>
       <c r="F15" s="3">
-        <v>42800</v>
+        <v>41600</v>
       </c>
       <c r="G15" s="3">
-        <v>26500</v>
+        <v>25700</v>
       </c>
       <c r="H15" s="3">
-        <v>16800</v>
+        <v>16400</v>
       </c>
       <c r="I15" s="3">
-        <v>9800</v>
+        <v>9500</v>
       </c>
       <c r="J15" s="3">
-        <v>5100</v>
+        <v>4900</v>
       </c>
       <c r="K15" s="3">
         <v>4700</v>
@@ -1051,25 +1051,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1917800</v>
+        <v>1865600</v>
       </c>
       <c r="E17" s="3">
-        <v>1753100</v>
+        <v>1705300</v>
       </c>
       <c r="F17" s="3">
-        <v>1500000</v>
+        <v>1459100</v>
       </c>
       <c r="G17" s="3">
-        <v>1049100</v>
+        <v>1020600</v>
       </c>
       <c r="H17" s="3">
-        <v>646500</v>
+        <v>628900</v>
       </c>
       <c r="I17" s="3">
-        <v>414900</v>
+        <v>403600</v>
       </c>
       <c r="J17" s="3">
-        <v>234700</v>
+        <v>228300</v>
       </c>
       <c r="K17" s="3">
         <v>180500</v>
@@ -1093,25 +1093,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>827800</v>
+        <v>805200</v>
       </c>
       <c r="E18" s="3">
-        <v>713000</v>
+        <v>693600</v>
       </c>
       <c r="F18" s="3">
-        <v>731400</v>
+        <v>711500</v>
       </c>
       <c r="G18" s="3">
-        <v>457000</v>
+        <v>444500</v>
       </c>
       <c r="H18" s="3">
-        <v>300900</v>
+        <v>292700</v>
       </c>
       <c r="I18" s="3">
-        <v>131700</v>
+        <v>128200</v>
       </c>
       <c r="J18" s="3">
-        <v>117600</v>
+        <v>114400</v>
       </c>
       <c r="K18" s="3">
         <v>76900</v>
@@ -1153,7 +1153,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>13600</v>
+        <v>13200</v>
       </c>
       <c r="E20" s="3">
         <v>-2200</v>
@@ -1168,10 +1168,10 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>-13400</v>
+        <v>-13000</v>
       </c>
       <c r="J20" s="3">
-        <v>-11300</v>
+        <v>-11000</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1195,25 +1195,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>888400</v>
+        <v>863300</v>
       </c>
       <c r="E21" s="3">
-        <v>749100</v>
+        <v>728000</v>
       </c>
       <c r="F21" s="3">
-        <v>773200</v>
+        <v>751300</v>
       </c>
       <c r="G21" s="3">
-        <v>483800</v>
+        <v>470100</v>
       </c>
       <c r="H21" s="3">
-        <v>317800</v>
+        <v>308800</v>
       </c>
       <c r="I21" s="3">
-        <v>128200</v>
+        <v>124500</v>
       </c>
       <c r="J21" s="3">
-        <v>111400</v>
+        <v>108300</v>
       </c>
       <c r="K21" s="3">
         <v>81600</v>
@@ -1237,19 +1237,19 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>114100</v>
+        <v>111000</v>
       </c>
       <c r="E22" s="3">
-        <v>74300</v>
+        <v>72300</v>
       </c>
       <c r="F22" s="3">
-        <v>25100</v>
+        <v>24400</v>
       </c>
       <c r="G22" s="3">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="H22" s="3">
-        <v>15600</v>
+        <v>15200</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
@@ -1279,25 +1279,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>727300</v>
+        <v>707500</v>
       </c>
       <c r="E23" s="3">
-        <v>636400</v>
+        <v>619100</v>
       </c>
       <c r="F23" s="3">
-        <v>704900</v>
+        <v>685700</v>
       </c>
       <c r="G23" s="3">
-        <v>447400</v>
+        <v>435200</v>
       </c>
       <c r="H23" s="3">
-        <v>285300</v>
+        <v>277500</v>
       </c>
       <c r="I23" s="3">
-        <v>118400</v>
+        <v>115200</v>
       </c>
       <c r="J23" s="3">
-        <v>106300</v>
+        <v>103400</v>
       </c>
       <c r="K23" s="3">
         <v>76900</v>
@@ -1321,25 +1321,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>6800</v>
+        <v>6600</v>
       </c>
       <c r="E24" s="3">
-        <v>-25000</v>
+        <v>-24400</v>
       </c>
       <c r="F24" s="3">
-        <v>41100</v>
+        <v>40000</v>
       </c>
       <c r="G24" s="3">
-        <v>62800</v>
+        <v>61100</v>
       </c>
       <c r="H24" s="3">
-        <v>84000</v>
+        <v>81700</v>
       </c>
       <c r="I24" s="3">
-        <v>32400</v>
+        <v>31500</v>
       </c>
       <c r="J24" s="3">
-        <v>28100</v>
+        <v>27300</v>
       </c>
       <c r="K24" s="3">
         <v>26800</v>
@@ -1405,25 +1405,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>720500</v>
+        <v>700800</v>
       </c>
       <c r="E26" s="3">
-        <v>661500</v>
+        <v>643500</v>
       </c>
       <c r="F26" s="3">
-        <v>663700</v>
+        <v>645700</v>
       </c>
       <c r="G26" s="3">
-        <v>384600</v>
+        <v>374100</v>
       </c>
       <c r="H26" s="3">
-        <v>201300</v>
+        <v>195800</v>
       </c>
       <c r="I26" s="3">
-        <v>86000</v>
+        <v>83600</v>
       </c>
       <c r="J26" s="3">
-        <v>78300</v>
+        <v>76100</v>
       </c>
       <c r="K26" s="3">
         <v>50100</v>
@@ -1447,25 +1447,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>720300</v>
+        <v>700700</v>
       </c>
       <c r="E27" s="3">
-        <v>661300</v>
+        <v>643300</v>
       </c>
       <c r="F27" s="3">
-        <v>663200</v>
+        <v>645100</v>
       </c>
       <c r="G27" s="3">
-        <v>383600</v>
+        <v>373200</v>
       </c>
       <c r="H27" s="3">
-        <v>199600</v>
+        <v>194200</v>
       </c>
       <c r="I27" s="3">
-        <v>85300</v>
+        <v>82900</v>
       </c>
       <c r="J27" s="3">
-        <v>76500</v>
+        <v>74400</v>
       </c>
       <c r="K27" s="3">
         <v>38800</v>
@@ -1657,7 +1657,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-13600</v>
+        <v>-13200</v>
       </c>
       <c r="E32" s="3">
         <v>2200</v>
@@ -1672,10 +1672,10 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>13400</v>
+        <v>13000</v>
       </c>
       <c r="J32" s="3">
-        <v>11300</v>
+        <v>11000</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -1699,25 +1699,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>720300</v>
+        <v>700700</v>
       </c>
       <c r="E33" s="3">
-        <v>661300</v>
+        <v>643300</v>
       </c>
       <c r="F33" s="3">
-        <v>663200</v>
+        <v>645100</v>
       </c>
       <c r="G33" s="3">
-        <v>383600</v>
+        <v>373200</v>
       </c>
       <c r="H33" s="3">
-        <v>199600</v>
+        <v>194200</v>
       </c>
       <c r="I33" s="3">
-        <v>85300</v>
+        <v>82900</v>
       </c>
       <c r="J33" s="3">
-        <v>76500</v>
+        <v>74400</v>
       </c>
       <c r="K33" s="3">
         <v>38800</v>
@@ -1783,25 +1783,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>720300</v>
+        <v>700700</v>
       </c>
       <c r="E35" s="3">
-        <v>661300</v>
+        <v>643300</v>
       </c>
       <c r="F35" s="3">
-        <v>663200</v>
+        <v>645100</v>
       </c>
       <c r="G35" s="3">
-        <v>383600</v>
+        <v>373200</v>
       </c>
       <c r="H35" s="3">
-        <v>199600</v>
+        <v>194200</v>
       </c>
       <c r="I35" s="3">
-        <v>85300</v>
+        <v>82900</v>
       </c>
       <c r="J35" s="3">
-        <v>76500</v>
+        <v>74400</v>
       </c>
       <c r="K35" s="3">
         <v>38800</v>
@@ -1908,25 +1908,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>728600</v>
+        <v>708700</v>
       </c>
       <c r="E41" s="3">
-        <v>656500</v>
+        <v>638600</v>
       </c>
       <c r="F41" s="3">
-        <v>459200</v>
+        <v>446700</v>
       </c>
       <c r="G41" s="3">
-        <v>361200</v>
+        <v>351300</v>
       </c>
       <c r="H41" s="3">
-        <v>20300</v>
+        <v>19800</v>
       </c>
       <c r="I41" s="3">
-        <v>12600</v>
+        <v>12300</v>
       </c>
       <c r="J41" s="3">
-        <v>28300</v>
+        <v>27500</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1992,25 +1992,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>171200</v>
+        <v>166500</v>
       </c>
       <c r="E43" s="3">
-        <v>140600</v>
+        <v>136800</v>
       </c>
       <c r="F43" s="3">
-        <v>115000</v>
+        <v>111900</v>
       </c>
       <c r="G43" s="3">
-        <v>117100</v>
+        <v>113900</v>
       </c>
       <c r="H43" s="3">
-        <v>130300</v>
+        <v>126800</v>
       </c>
       <c r="I43" s="3">
-        <v>74400</v>
+        <v>72400</v>
       </c>
       <c r="J43" s="3">
-        <v>31800</v>
+        <v>30900</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -2076,25 +2076,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>816300</v>
+        <v>794100</v>
       </c>
       <c r="E45" s="3">
-        <v>783400</v>
+        <v>762100</v>
       </c>
       <c r="F45" s="3">
-        <v>735900</v>
+        <v>715800</v>
       </c>
       <c r="G45" s="3">
-        <v>257500</v>
+        <v>250500</v>
       </c>
       <c r="H45" s="3">
-        <v>16600</v>
+        <v>16100</v>
       </c>
       <c r="I45" s="3">
-        <v>17900</v>
+        <v>17400</v>
       </c>
       <c r="J45" s="3">
-        <v>12100</v>
+        <v>11700</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -2160,25 +2160,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>33134700</v>
+        <v>32232600</v>
       </c>
       <c r="E47" s="3">
-        <v>27331100</v>
+        <v>26587000</v>
       </c>
       <c r="F47" s="3">
-        <v>19497000</v>
+        <v>18966200</v>
       </c>
       <c r="G47" s="3">
-        <v>14578800</v>
+        <v>14181900</v>
       </c>
       <c r="H47" s="3">
-        <v>6899300</v>
+        <v>6711400</v>
       </c>
       <c r="I47" s="3">
-        <v>2710700</v>
+        <v>2636900</v>
       </c>
       <c r="J47" s="3">
-        <v>1000300</v>
+        <v>973100</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -2202,25 +2202,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>121000</v>
+        <v>117800</v>
       </c>
       <c r="E48" s="3">
-        <v>105200</v>
+        <v>102300</v>
       </c>
       <c r="F48" s="3">
-        <v>110600</v>
+        <v>107600</v>
       </c>
       <c r="G48" s="3">
-        <v>71500</v>
+        <v>69600</v>
       </c>
       <c r="H48" s="3">
-        <v>68400</v>
+        <v>66500</v>
       </c>
       <c r="I48" s="3">
-        <v>18300</v>
+        <v>17800</v>
       </c>
       <c r="J48" s="3">
-        <v>8700</v>
+        <v>8500</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -2244,25 +2244,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>462300</v>
+        <v>449700</v>
       </c>
       <c r="E49" s="3">
-        <v>156000</v>
+        <v>151700</v>
       </c>
       <c r="F49" s="3">
-        <v>151700</v>
+        <v>147600</v>
       </c>
       <c r="G49" s="3">
-        <v>131800</v>
+        <v>128200</v>
       </c>
       <c r="H49" s="3">
-        <v>102300</v>
+        <v>99500</v>
       </c>
       <c r="I49" s="3">
-        <v>93300</v>
+        <v>90700</v>
       </c>
       <c r="J49" s="3">
-        <v>89300</v>
+        <v>86800</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2370,25 +2370,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>388800</v>
+        <v>378200</v>
       </c>
       <c r="E52" s="3">
-        <v>297800</v>
+        <v>289700</v>
       </c>
       <c r="F52" s="3">
-        <v>235200</v>
+        <v>228800</v>
       </c>
       <c r="G52" s="3">
-        <v>93300</v>
+        <v>90800</v>
       </c>
       <c r="H52" s="3">
-        <v>52600</v>
+        <v>51100</v>
       </c>
       <c r="I52" s="3">
-        <v>28200</v>
+        <v>27400</v>
       </c>
       <c r="J52" s="3">
-        <v>41800</v>
+        <v>40700</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2454,25 +2454,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>46012800</v>
+        <v>44760100</v>
       </c>
       <c r="E54" s="3">
-        <v>35480300</v>
+        <v>34514400</v>
       </c>
       <c r="F54" s="3">
-        <v>25744500</v>
+        <v>25043700</v>
       </c>
       <c r="G54" s="3">
-        <v>17742300</v>
+        <v>17259300</v>
       </c>
       <c r="H54" s="3">
-        <v>8059700</v>
+        <v>7840300</v>
       </c>
       <c r="I54" s="3">
-        <v>3274700</v>
+        <v>3185600</v>
       </c>
       <c r="J54" s="3">
-        <v>1318500</v>
+        <v>1282600</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2532,25 +2532,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>175200</v>
+        <v>170400</v>
       </c>
       <c r="E57" s="3">
-        <v>114100</v>
+        <v>111000</v>
       </c>
       <c r="F57" s="3">
-        <v>160300</v>
+        <v>155900</v>
       </c>
       <c r="G57" s="3">
-        <v>158800</v>
+        <v>154500</v>
       </c>
       <c r="H57" s="3">
-        <v>49300</v>
+        <v>48000</v>
       </c>
       <c r="I57" s="3">
-        <v>24900</v>
+        <v>24200</v>
       </c>
       <c r="J57" s="3">
-        <v>13200</v>
+        <v>12900</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2574,25 +2574,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>10771400</v>
+        <v>10478200</v>
       </c>
       <c r="E58" s="3">
-        <v>9105600</v>
+        <v>8857700</v>
       </c>
       <c r="F58" s="3">
-        <v>5686300</v>
+        <v>5531500</v>
       </c>
       <c r="G58" s="3">
-        <v>6340100</v>
+        <v>6167500</v>
       </c>
       <c r="H58" s="3">
-        <v>3353000</v>
+        <v>3261800</v>
       </c>
       <c r="I58" s="3">
-        <v>1480800</v>
+        <v>1440500</v>
       </c>
       <c r="J58" s="3">
-        <v>250700</v>
+        <v>243900</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2616,25 +2616,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>315200</v>
+        <v>306600</v>
       </c>
       <c r="E59" s="3">
-        <v>246400</v>
+        <v>239700</v>
       </c>
       <c r="F59" s="3">
-        <v>290400</v>
+        <v>282500</v>
       </c>
       <c r="G59" s="3">
-        <v>203800</v>
+        <v>198300</v>
       </c>
       <c r="H59" s="3">
-        <v>154800</v>
+        <v>150600</v>
       </c>
       <c r="I59" s="3">
-        <v>65600</v>
+        <v>63800</v>
       </c>
       <c r="J59" s="3">
-        <v>65800</v>
+        <v>64000</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2700,25 +2700,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>647100</v>
+        <v>629500</v>
       </c>
       <c r="E61" s="3">
-        <v>697900</v>
+        <v>678900</v>
       </c>
       <c r="F61" s="3">
-        <v>847800</v>
+        <v>824700</v>
       </c>
       <c r="G61" s="3">
-        <v>108800</v>
+        <v>105900</v>
       </c>
       <c r="H61" s="3">
-        <v>181900</v>
+        <v>177000</v>
       </c>
       <c r="I61" s="3">
-        <v>140700</v>
+        <v>136900</v>
       </c>
       <c r="J61" s="3">
-        <v>136100</v>
+        <v>132400</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2742,22 +2742,22 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>10456100</v>
+        <v>10171500</v>
       </c>
       <c r="E62" s="3">
-        <v>8478300</v>
+        <v>8247500</v>
       </c>
       <c r="F62" s="3">
-        <v>5908600</v>
+        <v>5747700</v>
       </c>
       <c r="G62" s="3">
-        <v>2478700</v>
+        <v>2411300</v>
       </c>
       <c r="H62" s="3">
-        <v>698300</v>
+        <v>679300</v>
       </c>
       <c r="I62" s="3">
-        <v>5500</v>
+        <v>5300</v>
       </c>
       <c r="J62" s="3">
         <v>3400</v>
@@ -2910,25 +2910,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>42419300</v>
+        <v>41264400</v>
       </c>
       <c r="E66" s="3">
-        <v>32332800</v>
+        <v>31452500</v>
       </c>
       <c r="F66" s="3">
-        <v>23080900</v>
+        <v>22452500</v>
       </c>
       <c r="G66" s="3">
-        <v>15729500</v>
+        <v>15301200</v>
       </c>
       <c r="H66" s="3">
-        <v>6738100</v>
+        <v>6554600</v>
       </c>
       <c r="I66" s="3">
-        <v>2889600</v>
+        <v>2810900</v>
       </c>
       <c r="J66" s="3">
-        <v>1107100</v>
+        <v>1077000</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -3138,25 +3138,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>3545500</v>
+        <v>3449000</v>
       </c>
       <c r="E72" s="3">
-        <v>3539300</v>
+        <v>3443000</v>
       </c>
       <c r="F72" s="3">
-        <v>2757200</v>
+        <v>2682200</v>
       </c>
       <c r="G72" s="3">
-        <v>1970300</v>
+        <v>1916600</v>
       </c>
       <c r="H72" s="3">
-        <v>1282900</v>
+        <v>1247900</v>
       </c>
       <c r="I72" s="3">
-        <v>175100</v>
+        <v>170300</v>
       </c>
       <c r="J72" s="3">
-        <v>126700</v>
+        <v>123200</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -3306,25 +3306,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3593500</v>
+        <v>3495600</v>
       </c>
       <c r="E76" s="3">
-        <v>3147500</v>
+        <v>3061800</v>
       </c>
       <c r="F76" s="3">
-        <v>2663700</v>
+        <v>2591100</v>
       </c>
       <c r="G76" s="3">
-        <v>2012900</v>
+        <v>1958100</v>
       </c>
       <c r="H76" s="3">
-        <v>1321700</v>
+        <v>1285700</v>
       </c>
       <c r="I76" s="3">
-        <v>385200</v>
+        <v>374700</v>
       </c>
       <c r="J76" s="3">
-        <v>211300</v>
+        <v>205600</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -3437,25 +3437,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>720300</v>
+        <v>700700</v>
       </c>
       <c r="E81" s="3">
-        <v>661300</v>
+        <v>643300</v>
       </c>
       <c r="F81" s="3">
-        <v>663200</v>
+        <v>645100</v>
       </c>
       <c r="G81" s="3">
-        <v>383600</v>
+        <v>373200</v>
       </c>
       <c r="H81" s="3">
-        <v>199600</v>
+        <v>194200</v>
       </c>
       <c r="I81" s="3">
-        <v>85300</v>
+        <v>82900</v>
       </c>
       <c r="J81" s="3">
-        <v>76500</v>
+        <v>74400</v>
       </c>
       <c r="K81" s="3">
         <v>38800</v>
@@ -3497,25 +3497,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>46600</v>
+        <v>45400</v>
       </c>
       <c r="E83" s="3">
-        <v>38000</v>
+        <v>37000</v>
       </c>
       <c r="F83" s="3">
-        <v>42800</v>
+        <v>41600</v>
       </c>
       <c r="G83" s="3">
-        <v>26500</v>
+        <v>25700</v>
       </c>
       <c r="H83" s="3">
-        <v>16800</v>
+        <v>16300</v>
       </c>
       <c r="I83" s="3">
-        <v>9800</v>
+        <v>9500</v>
       </c>
       <c r="J83" s="3">
-        <v>5100</v>
+        <v>4900</v>
       </c>
       <c r="K83" s="3">
         <v>4700</v>
@@ -3749,25 +3749,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1501600</v>
+        <v>1460700</v>
       </c>
       <c r="E89" s="3">
-        <v>333300</v>
+        <v>324200</v>
       </c>
       <c r="F89" s="3">
-        <v>-742800</v>
+        <v>-722600</v>
       </c>
       <c r="G89" s="3">
-        <v>279100</v>
+        <v>271500</v>
       </c>
       <c r="H89" s="3">
-        <v>-704700</v>
+        <v>-685500</v>
       </c>
       <c r="I89" s="3">
-        <v>-84400</v>
+        <v>-82100</v>
       </c>
       <c r="J89" s="3">
-        <v>48500</v>
+        <v>47200</v>
       </c>
       <c r="K89" s="3">
         <v>1000</v>
@@ -3809,25 +3809,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-12200</v>
+        <v>-11900</v>
       </c>
       <c r="E91" s="3">
-        <v>-8200</v>
+        <v>-8000</v>
       </c>
       <c r="F91" s="3">
-        <v>-25000</v>
+        <v>-24300</v>
       </c>
       <c r="G91" s="3">
-        <v>-26800</v>
+        <v>-26100</v>
       </c>
       <c r="H91" s="3">
-        <v>-13400</v>
+        <v>-13000</v>
       </c>
       <c r="I91" s="3">
-        <v>-9900</v>
+        <v>-9600</v>
       </c>
       <c r="J91" s="3">
-        <v>-3800</v>
+        <v>-3700</v>
       </c>
       <c r="K91" s="3">
         <v>-2600</v>
@@ -3935,25 +3935,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>99600</v>
+        <v>96800</v>
       </c>
       <c r="E94" s="3">
-        <v>-68600</v>
+        <v>-66700</v>
       </c>
       <c r="F94" s="3">
-        <v>-212600</v>
+        <v>-206800</v>
       </c>
       <c r="G94" s="3">
-        <v>-107500</v>
+        <v>-104600</v>
       </c>
       <c r="H94" s="3">
-        <v>-29800</v>
+        <v>-29000</v>
       </c>
       <c r="I94" s="3">
-        <v>-27200</v>
+        <v>-26400</v>
       </c>
       <c r="J94" s="3">
-        <v>-84200</v>
+        <v>-81900</v>
       </c>
       <c r="K94" s="3">
         <v>-6500</v>
@@ -3995,7 +3995,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-654500</v>
+        <v>-636700</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -4007,13 +4007,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-92400</v>
+        <v>-89900</v>
       </c>
       <c r="I96" s="3">
-        <v>-60000</v>
+        <v>-58400</v>
       </c>
       <c r="J96" s="3">
-        <v>-35100</v>
+        <v>-34100</v>
       </c>
       <c r="K96" s="3">
         <v>-35900</v>
@@ -4163,25 +4163,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-812000</v>
+        <v>-789900</v>
       </c>
       <c r="E100" s="3">
-        <v>-37000</v>
+        <v>-36000</v>
       </c>
       <c r="F100" s="3">
-        <v>1226700</v>
+        <v>1193300</v>
       </c>
       <c r="G100" s="3">
-        <v>145700</v>
+        <v>141800</v>
       </c>
       <c r="H100" s="3">
-        <v>782200</v>
+        <v>761000</v>
       </c>
       <c r="I100" s="3">
-        <v>70200</v>
+        <v>68300</v>
       </c>
       <c r="J100" s="3">
-        <v>108000</v>
+        <v>105100</v>
       </c>
       <c r="K100" s="3">
         <v>16900</v>
@@ -4205,25 +4205,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-5200</v>
+        <v>-5100</v>
       </c>
       <c r="E101" s="3">
-        <v>-3100</v>
+        <v>-3000</v>
       </c>
       <c r="F101" s="3">
-        <v>-69600</v>
+        <v>-67700</v>
       </c>
       <c r="G101" s="3">
-        <v>10200</v>
+        <v>9900</v>
       </c>
       <c r="H101" s="3">
         <v>500</v>
       </c>
       <c r="I101" s="3">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="J101" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="K101" s="3">
         <v>-1500</v>
@@ -4247,25 +4247,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>783900</v>
+        <v>762600</v>
       </c>
       <c r="E102" s="3">
-        <v>224600</v>
+        <v>218500</v>
       </c>
       <c r="F102" s="3">
-        <v>201700</v>
+        <v>196200</v>
       </c>
       <c r="G102" s="3">
-        <v>327500</v>
+        <v>318600</v>
       </c>
       <c r="H102" s="3">
-        <v>48200</v>
+        <v>46900</v>
       </c>
       <c r="I102" s="3">
-        <v>-38500</v>
+        <v>-37500</v>
       </c>
       <c r="J102" s="3">
-        <v>73000</v>
+        <v>71100</v>
       </c>
       <c r="K102" s="3">
         <v>9900</v>

--- a/AAII_Financials/Yearly/XP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/XP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="92">
   <si>
     <t>XP</t>
   </si>
@@ -724,25 +724,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>2670800</v>
+        <v>2935200</v>
       </c>
       <c r="E8" s="3">
-        <v>2398900</v>
+        <v>2448700</v>
       </c>
       <c r="F8" s="3">
-        <v>2170600</v>
+        <v>2143200</v>
       </c>
       <c r="G8" s="3">
-        <v>1465100</v>
+        <v>1559500</v>
       </c>
       <c r="H8" s="3">
-        <v>921600</v>
+        <v>1254700</v>
       </c>
       <c r="I8" s="3">
-        <v>531700</v>
+        <v>745500</v>
       </c>
       <c r="J8" s="3">
-        <v>342700</v>
+        <v>557100</v>
       </c>
       <c r="K8" s="3">
         <v>257400</v>
@@ -765,26 +765,26 @@
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>906600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>732200</v>
+      </c>
+      <c r="F9" s="3">
+        <v>615600</v>
+      </c>
+      <c r="G9" s="3">
+        <v>509400</v>
+      </c>
+      <c r="H9" s="3">
+        <v>397200</v>
+      </c>
+      <c r="I9" s="3">
+        <v>241000</v>
+      </c>
+      <c r="J9" s="3">
+        <v>175100</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -807,26 +807,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>2028700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1716400</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1527600</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1050100</v>
+      </c>
+      <c r="H10" s="3">
+        <v>857500</v>
+      </c>
+      <c r="I10" s="3">
+        <v>504500</v>
+      </c>
+      <c r="J10" s="3">
+        <v>382100</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -952,25 +952,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>14000</v>
+        <v>25600</v>
       </c>
       <c r="E14" s="3">
-        <v>1200</v>
+        <v>2900</v>
       </c>
       <c r="F14" s="3">
-        <v>800</v>
+        <v>1400</v>
       </c>
       <c r="G14" s="3">
-        <v>9400</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+        <v>18800</v>
+      </c>
+      <c r="H14" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I14" s="3">
+        <v>7100</v>
+      </c>
+      <c r="J14" s="3">
+        <v>6200</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -994,25 +994,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>45400</v>
+        <v>21600</v>
       </c>
       <c r="E15" s="3">
-        <v>37000</v>
+        <v>9500</v>
       </c>
       <c r="F15" s="3">
-        <v>41600</v>
+        <v>14900</v>
       </c>
       <c r="G15" s="3">
-        <v>25700</v>
+        <v>16600</v>
       </c>
       <c r="H15" s="3">
-        <v>16400</v>
+        <v>17200</v>
       </c>
       <c r="I15" s="3">
-        <v>9500</v>
+        <v>9800</v>
       </c>
       <c r="J15" s="3">
-        <v>4900</v>
+        <v>6200</v>
       </c>
       <c r="K15" s="3">
         <v>4700</v>
@@ -1051,25 +1051,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1865600</v>
+        <v>2113600</v>
       </c>
       <c r="E17" s="3">
-        <v>1705300</v>
+        <v>1791900</v>
       </c>
       <c r="F17" s="3">
-        <v>1459100</v>
+        <v>1455700</v>
       </c>
       <c r="G17" s="3">
-        <v>1020600</v>
+        <v>1074700</v>
       </c>
       <c r="H17" s="3">
-        <v>628900</v>
+        <v>865600</v>
       </c>
       <c r="I17" s="3">
-        <v>403600</v>
+        <v>572900</v>
       </c>
       <c r="J17" s="3">
-        <v>228300</v>
+        <v>377200</v>
       </c>
       <c r="K17" s="3">
         <v>180500</v>
@@ -1093,25 +1093,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>805200</v>
+        <v>821600</v>
       </c>
       <c r="E18" s="3">
-        <v>693600</v>
+        <v>656800</v>
       </c>
       <c r="F18" s="3">
-        <v>711500</v>
+        <v>687600</v>
       </c>
       <c r="G18" s="3">
-        <v>444500</v>
+        <v>484900</v>
       </c>
       <c r="H18" s="3">
-        <v>292700</v>
+        <v>389100</v>
       </c>
       <c r="I18" s="3">
-        <v>128200</v>
+        <v>172600</v>
       </c>
       <c r="J18" s="3">
-        <v>114400</v>
+        <v>179900</v>
       </c>
       <c r="K18" s="3">
         <v>76900</v>
@@ -1153,25 +1153,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>13200</v>
+        <v>-15100</v>
       </c>
       <c r="E20" s="3">
-        <v>-2200</v>
+        <v>2300</v>
       </c>
       <c r="F20" s="3">
-        <v>-1400</v>
+        <v>1400</v>
       </c>
       <c r="G20" s="3">
-        <v>200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-13000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-11000</v>
+        <v>-200</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1195,25 +1195,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>863300</v>
+        <v>858400</v>
       </c>
       <c r="E21" s="3">
-        <v>728000</v>
+        <v>664000</v>
       </c>
       <c r="F21" s="3">
-        <v>751300</v>
+        <v>701100</v>
       </c>
       <c r="G21" s="3">
-        <v>470100</v>
+        <v>501600</v>
       </c>
       <c r="H21" s="3">
-        <v>308800</v>
+        <v>406300</v>
       </c>
       <c r="I21" s="3">
-        <v>124500</v>
+        <v>182400</v>
       </c>
       <c r="J21" s="3">
-        <v>108300</v>
+        <v>186100</v>
       </c>
       <c r="K21" s="3">
         <v>81600</v>
@@ -1236,20 +1236,20 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>111000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>72300</v>
-      </c>
-      <c r="F22" s="3">
-        <v>24400</v>
-      </c>
-      <c r="G22" s="3">
-        <v>9500</v>
-      </c>
-      <c r="H22" s="3">
-        <v>15200</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
@@ -1279,25 +1279,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>707500</v>
+        <v>811200</v>
       </c>
       <c r="E23" s="3">
-        <v>619100</v>
+        <v>651600</v>
       </c>
       <c r="F23" s="3">
-        <v>685700</v>
+        <v>684700</v>
       </c>
       <c r="G23" s="3">
-        <v>435200</v>
+        <v>466300</v>
       </c>
       <c r="H23" s="3">
-        <v>277500</v>
+        <v>384100</v>
       </c>
       <c r="I23" s="3">
-        <v>115200</v>
+        <v>165500</v>
       </c>
       <c r="J23" s="3">
-        <v>103400</v>
+        <v>173700</v>
       </c>
       <c r="K23" s="3">
         <v>76900</v>
@@ -1321,25 +1321,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>6600</v>
+        <v>7600</v>
       </c>
       <c r="E24" s="3">
-        <v>-24400</v>
+        <v>-25600</v>
       </c>
       <c r="F24" s="3">
         <v>40000</v>
       </c>
       <c r="G24" s="3">
-        <v>61100</v>
+        <v>65500</v>
       </c>
       <c r="H24" s="3">
-        <v>81700</v>
+        <v>113100</v>
       </c>
       <c r="I24" s="3">
-        <v>31500</v>
+        <v>45300</v>
       </c>
       <c r="J24" s="3">
-        <v>27300</v>
+        <v>45900</v>
       </c>
       <c r="K24" s="3">
         <v>26800</v>
@@ -1405,25 +1405,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>700800</v>
+        <v>803600</v>
       </c>
       <c r="E26" s="3">
-        <v>643500</v>
+        <v>677200</v>
       </c>
       <c r="F26" s="3">
-        <v>645700</v>
+        <v>644800</v>
       </c>
       <c r="G26" s="3">
-        <v>374100</v>
+        <v>400800</v>
       </c>
       <c r="H26" s="3">
-        <v>195800</v>
+        <v>271000</v>
       </c>
       <c r="I26" s="3">
-        <v>83600</v>
+        <v>120200</v>
       </c>
       <c r="J26" s="3">
-        <v>76100</v>
+        <v>127900</v>
       </c>
       <c r="K26" s="3">
         <v>50100</v>
@@ -1447,25 +1447,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>700700</v>
+        <v>803500</v>
       </c>
       <c r="E27" s="3">
-        <v>643300</v>
+        <v>677000</v>
       </c>
       <c r="F27" s="3">
-        <v>645100</v>
+        <v>644200</v>
       </c>
       <c r="G27" s="3">
-        <v>373200</v>
+        <v>399800</v>
       </c>
       <c r="H27" s="3">
-        <v>194200</v>
+        <v>268800</v>
       </c>
       <c r="I27" s="3">
-        <v>82900</v>
+        <v>119200</v>
       </c>
       <c r="J27" s="3">
-        <v>74400</v>
+        <v>124900</v>
       </c>
       <c r="K27" s="3">
         <v>38800</v>
@@ -1657,25 +1657,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-13200</v>
+        <v>15100</v>
       </c>
       <c r="E32" s="3">
-        <v>2200</v>
+        <v>-2300</v>
       </c>
       <c r="F32" s="3">
-        <v>1400</v>
+        <v>-1400</v>
       </c>
       <c r="G32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>13000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>11000</v>
+        <v>200</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -1699,25 +1699,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>700700</v>
+        <v>803500</v>
       </c>
       <c r="E33" s="3">
-        <v>643300</v>
+        <v>677000</v>
       </c>
       <c r="F33" s="3">
-        <v>645100</v>
+        <v>644200</v>
       </c>
       <c r="G33" s="3">
-        <v>373200</v>
+        <v>399800</v>
       </c>
       <c r="H33" s="3">
-        <v>194200</v>
+        <v>268800</v>
       </c>
       <c r="I33" s="3">
-        <v>82900</v>
+        <v>119200</v>
       </c>
       <c r="J33" s="3">
-        <v>74400</v>
+        <v>124900</v>
       </c>
       <c r="K33" s="3">
         <v>38800</v>
@@ -1783,25 +1783,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>700700</v>
+        <v>803500</v>
       </c>
       <c r="E35" s="3">
-        <v>643300</v>
+        <v>677000</v>
       </c>
       <c r="F35" s="3">
-        <v>645100</v>
+        <v>644200</v>
       </c>
       <c r="G35" s="3">
-        <v>373200</v>
+        <v>399800</v>
       </c>
       <c r="H35" s="3">
-        <v>194200</v>
+        <v>268800</v>
       </c>
       <c r="I35" s="3">
-        <v>82900</v>
+        <v>119200</v>
       </c>
       <c r="J35" s="3">
-        <v>74400</v>
+        <v>124900</v>
       </c>
       <c r="K35" s="3">
         <v>38800</v>
@@ -1908,25 +1908,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>708700</v>
+        <v>812700</v>
       </c>
       <c r="E41" s="3">
-        <v>638600</v>
+        <v>672100</v>
       </c>
       <c r="F41" s="3">
-        <v>446700</v>
+        <v>446100</v>
       </c>
       <c r="G41" s="3">
-        <v>351300</v>
+        <v>376400</v>
       </c>
       <c r="H41" s="3">
-        <v>19800</v>
+        <v>27300</v>
       </c>
       <c r="I41" s="3">
-        <v>12300</v>
+        <v>17700</v>
       </c>
       <c r="J41" s="3">
-        <v>27500</v>
+        <v>46300</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1950,25 +1950,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>29087000</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>19410700</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>13938600</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>12209100</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>8899300</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>3715000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>1503100</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -1992,25 +1992,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>166500</v>
+        <v>6035100</v>
       </c>
       <c r="E43" s="3">
-        <v>136800</v>
+        <v>4318200</v>
       </c>
       <c r="F43" s="3">
-        <v>111900</v>
+        <v>2386100</v>
       </c>
       <c r="G43" s="3">
-        <v>113900</v>
+        <v>852900</v>
       </c>
       <c r="H43" s="3">
-        <v>126800</v>
+        <v>119300</v>
       </c>
       <c r="I43" s="3">
-        <v>72400</v>
+        <v>56800</v>
       </c>
       <c r="J43" s="3">
-        <v>30900</v>
+        <v>47200</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -2033,26 +2033,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2076,25 +2076,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>794100</v>
+        <v>972400</v>
       </c>
       <c r="E45" s="3">
-        <v>762100</v>
+        <v>1120100</v>
       </c>
       <c r="F45" s="3">
-        <v>715800</v>
+        <v>388000</v>
       </c>
       <c r="G45" s="3">
-        <v>250500</v>
+        <v>352400</v>
       </c>
       <c r="H45" s="3">
-        <v>16100</v>
+        <v>257400</v>
       </c>
       <c r="I45" s="3">
-        <v>17400</v>
+        <v>338100</v>
       </c>
       <c r="J45" s="3">
-        <v>11700</v>
+        <v>313100</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -2118,25 +2118,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>36907200</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>25521100</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>17158800</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>13790900</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>9303300</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>4127600</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>1909700</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2160,25 +2160,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>32232600</v>
+        <v>12001700</v>
       </c>
       <c r="E47" s="3">
-        <v>26587000</v>
+        <v>9370800</v>
       </c>
       <c r="F47" s="3">
-        <v>18966200</v>
+        <v>6649000</v>
       </c>
       <c r="G47" s="3">
-        <v>14181900</v>
+        <v>4166500</v>
       </c>
       <c r="H47" s="3">
-        <v>6711400</v>
+        <v>1219700</v>
       </c>
       <c r="I47" s="3">
-        <v>2636900</v>
-      </c>
-      <c r="J47" s="3">
-        <v>973100</v>
+        <v>235400</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -2202,25 +2202,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>117800</v>
+        <v>135000</v>
       </c>
       <c r="E48" s="3">
-        <v>102300</v>
+        <v>107700</v>
       </c>
       <c r="F48" s="3">
-        <v>107600</v>
+        <v>107400</v>
       </c>
       <c r="G48" s="3">
-        <v>69600</v>
+        <v>74600</v>
       </c>
       <c r="H48" s="3">
-        <v>66500</v>
+        <v>92000</v>
       </c>
       <c r="I48" s="3">
-        <v>17800</v>
+        <v>25600</v>
       </c>
       <c r="J48" s="3">
-        <v>8500</v>
+        <v>14200</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -2244,25 +2244,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>449700</v>
+        <v>515600</v>
       </c>
       <c r="E49" s="3">
-        <v>151700</v>
+        <v>159700</v>
       </c>
       <c r="F49" s="3">
-        <v>147600</v>
+        <v>147300</v>
       </c>
       <c r="G49" s="3">
-        <v>128200</v>
+        <v>137400</v>
       </c>
       <c r="H49" s="3">
-        <v>99500</v>
+        <v>137700</v>
       </c>
       <c r="I49" s="3">
-        <v>90700</v>
+        <v>130400</v>
       </c>
       <c r="J49" s="3">
-        <v>86800</v>
+        <v>145900</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2370,25 +2370,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>378200</v>
+        <v>1331100</v>
       </c>
       <c r="E52" s="3">
-        <v>289700</v>
+        <v>860600</v>
       </c>
       <c r="F52" s="3">
-        <v>228800</v>
+        <v>717600</v>
       </c>
       <c r="G52" s="3">
-        <v>90800</v>
+        <v>224700</v>
       </c>
       <c r="H52" s="3">
-        <v>51100</v>
+        <v>28900</v>
       </c>
       <c r="I52" s="3">
-        <v>27400</v>
+        <v>19900</v>
       </c>
       <c r="J52" s="3">
-        <v>40700</v>
+        <v>16100</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2454,25 +2454,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>44760100</v>
+        <v>51324300</v>
       </c>
       <c r="E54" s="3">
-        <v>34514400</v>
+        <v>36324800</v>
       </c>
       <c r="F54" s="3">
-        <v>25043700</v>
+        <v>25008600</v>
       </c>
       <c r="G54" s="3">
-        <v>17259300</v>
+        <v>18491300</v>
       </c>
       <c r="H54" s="3">
-        <v>7840300</v>
+        <v>10852500</v>
       </c>
       <c r="I54" s="3">
-        <v>3185600</v>
+        <v>4578400</v>
       </c>
       <c r="J54" s="3">
-        <v>1282600</v>
+        <v>2154200</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2532,25 +2532,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>170400</v>
+        <v>195400</v>
       </c>
       <c r="E57" s="3">
-        <v>111000</v>
+        <v>116800</v>
       </c>
       <c r="F57" s="3">
-        <v>155900</v>
+        <v>155700</v>
       </c>
       <c r="G57" s="3">
-        <v>154500</v>
+        <v>165500</v>
       </c>
       <c r="H57" s="3">
-        <v>48000</v>
+        <v>66400</v>
       </c>
       <c r="I57" s="3">
-        <v>24200</v>
+        <v>34800</v>
       </c>
       <c r="J57" s="3">
-        <v>12900</v>
+        <v>21600</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2574,25 +2574,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>10478200</v>
+        <v>16994300</v>
       </c>
       <c r="E58" s="3">
-        <v>8857700</v>
+        <v>10577100</v>
       </c>
       <c r="F58" s="3">
-        <v>5531500</v>
+        <v>7588300</v>
       </c>
       <c r="G58" s="3">
-        <v>6167500</v>
+        <v>8117300</v>
       </c>
       <c r="H58" s="3">
-        <v>3261800</v>
+        <v>5334100</v>
       </c>
       <c r="I58" s="3">
-        <v>1440500</v>
+        <v>2309200</v>
       </c>
       <c r="J58" s="3">
-        <v>243900</v>
+        <v>496200</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2616,25 +2616,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>306600</v>
+        <v>9333500</v>
       </c>
       <c r="E59" s="3">
-        <v>239700</v>
+        <v>7671600</v>
       </c>
       <c r="F59" s="3">
-        <v>282500</v>
+        <v>4702700</v>
       </c>
       <c r="G59" s="3">
-        <v>198300</v>
+        <v>3981400</v>
       </c>
       <c r="H59" s="3">
-        <v>150600</v>
+        <v>2353000</v>
       </c>
       <c r="I59" s="3">
-        <v>63800</v>
+        <v>1397400</v>
       </c>
       <c r="J59" s="3">
-        <v>64000</v>
+        <v>994400</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2658,25 +2658,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>26828200</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>18590600</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>12679700</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>12426400</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>7896200</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>3808100</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>1567100</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2700,25 +2700,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>629500</v>
+        <v>4942500</v>
       </c>
       <c r="E61" s="3">
-        <v>678900</v>
+        <v>3743900</v>
       </c>
       <c r="F61" s="3">
-        <v>824700</v>
+        <v>2724600</v>
       </c>
       <c r="G61" s="3">
-        <v>105900</v>
+        <v>697500</v>
       </c>
       <c r="H61" s="3">
-        <v>177000</v>
+        <v>234000</v>
       </c>
       <c r="I61" s="3">
-        <v>136900</v>
+        <v>214000</v>
       </c>
       <c r="J61" s="3">
-        <v>132400</v>
+        <v>233800</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2742,25 +2742,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>10171500</v>
+        <v>3901900</v>
       </c>
       <c r="E62" s="3">
-        <v>8247500</v>
+        <v>2094700</v>
       </c>
       <c r="F62" s="3">
-        <v>5747700</v>
+        <v>1281900</v>
       </c>
       <c r="G62" s="3">
-        <v>2411300</v>
+        <v>689500</v>
       </c>
       <c r="H62" s="3">
-        <v>679300</v>
+        <v>5600</v>
       </c>
       <c r="I62" s="3">
-        <v>5300</v>
+        <v>8700</v>
       </c>
       <c r="J62" s="3">
-        <v>3400</v>
+        <v>3600</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2910,25 +2910,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>41264400</v>
+        <v>47315700</v>
       </c>
       <c r="E66" s="3">
-        <v>31452500</v>
+        <v>33101100</v>
       </c>
       <c r="F66" s="3">
-        <v>22452500</v>
+        <v>22420600</v>
       </c>
       <c r="G66" s="3">
-        <v>15301200</v>
+        <v>16392900</v>
       </c>
       <c r="H66" s="3">
-        <v>6554600</v>
+        <v>9072200</v>
       </c>
       <c r="I66" s="3">
-        <v>2810900</v>
+        <v>4038100</v>
       </c>
       <c r="J66" s="3">
-        <v>1077000</v>
+        <v>1806500</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -3137,26 +3137,26 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>3449000</v>
-      </c>
-      <c r="E72" s="3">
-        <v>3443000</v>
-      </c>
-      <c r="F72" s="3">
-        <v>2682200</v>
-      </c>
-      <c r="G72" s="3">
-        <v>1916600</v>
-      </c>
-      <c r="H72" s="3">
-        <v>1247900</v>
-      </c>
-      <c r="I72" s="3">
-        <v>170300</v>
+      <c r="D72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J72" s="3">
-        <v>123200</v>
+        <v>45400</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -3306,25 +3306,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3495600</v>
+        <v>4008300</v>
       </c>
       <c r="E76" s="3">
-        <v>3061800</v>
+        <v>3222400</v>
       </c>
       <c r="F76" s="3">
-        <v>2591100</v>
+        <v>2587500</v>
       </c>
       <c r="G76" s="3">
-        <v>1958100</v>
+        <v>2097900</v>
       </c>
       <c r="H76" s="3">
-        <v>1285700</v>
+        <v>1779600</v>
       </c>
       <c r="I76" s="3">
-        <v>374700</v>
+        <v>538500</v>
       </c>
       <c r="J76" s="3">
-        <v>205600</v>
+        <v>345300</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -3437,25 +3437,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>700700</v>
+        <v>803500</v>
       </c>
       <c r="E81" s="3">
-        <v>643300</v>
+        <v>677000</v>
       </c>
       <c r="F81" s="3">
-        <v>645100</v>
+        <v>644200</v>
       </c>
       <c r="G81" s="3">
-        <v>373200</v>
+        <v>399800</v>
       </c>
       <c r="H81" s="3">
-        <v>194200</v>
+        <v>268800</v>
       </c>
       <c r="I81" s="3">
-        <v>82900</v>
+        <v>119200</v>
       </c>
       <c r="J81" s="3">
-        <v>74400</v>
+        <v>124900</v>
       </c>
       <c r="K81" s="3">
         <v>38800</v>
@@ -3497,25 +3497,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>45400</v>
+        <v>24400</v>
       </c>
       <c r="E83" s="3">
-        <v>37000</v>
+        <v>20900</v>
       </c>
       <c r="F83" s="3">
-        <v>41600</v>
+        <v>12300</v>
       </c>
       <c r="G83" s="3">
-        <v>25700</v>
+        <v>13000</v>
       </c>
       <c r="H83" s="3">
-        <v>16300</v>
+        <v>13200</v>
       </c>
       <c r="I83" s="3">
-        <v>9500</v>
+        <v>6300</v>
       </c>
       <c r="J83" s="3">
-        <v>4900</v>
+        <v>2800</v>
       </c>
       <c r="K83" s="3">
         <v>4700</v>
@@ -3749,25 +3749,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1460700</v>
+        <v>1674900</v>
       </c>
       <c r="E89" s="3">
-        <v>324200</v>
+        <v>341200</v>
       </c>
       <c r="F89" s="3">
-        <v>-722600</v>
+        <v>-721600</v>
       </c>
       <c r="G89" s="3">
-        <v>271500</v>
+        <v>290900</v>
       </c>
       <c r="H89" s="3">
-        <v>-685500</v>
+        <v>-948800</v>
       </c>
       <c r="I89" s="3">
-        <v>-82100</v>
+        <v>-118000</v>
       </c>
       <c r="J89" s="3">
-        <v>47200</v>
+        <v>79200</v>
       </c>
       <c r="K89" s="3">
         <v>1000</v>
@@ -3809,25 +3809,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-11900</v>
+        <v>-13600</v>
       </c>
       <c r="E91" s="3">
-        <v>-8000</v>
+        <v>-8400</v>
       </c>
       <c r="F91" s="3">
         <v>-24300</v>
       </c>
       <c r="G91" s="3">
-        <v>-26100</v>
+        <v>-28000</v>
       </c>
       <c r="H91" s="3">
-        <v>-13000</v>
+        <v>-18000</v>
       </c>
       <c r="I91" s="3">
-        <v>-9600</v>
+        <v>-21500</v>
       </c>
       <c r="J91" s="3">
-        <v>-3700</v>
+        <v>-9200</v>
       </c>
       <c r="K91" s="3">
         <v>-2600</v>
@@ -3935,25 +3935,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>96800</v>
+        <v>111000</v>
       </c>
       <c r="E94" s="3">
-        <v>-66700</v>
+        <v>-70200</v>
       </c>
       <c r="F94" s="3">
-        <v>-206800</v>
+        <v>-206500</v>
       </c>
       <c r="G94" s="3">
-        <v>-104600</v>
+        <v>-112100</v>
       </c>
       <c r="H94" s="3">
-        <v>-29000</v>
+        <v>-40200</v>
       </c>
       <c r="I94" s="3">
-        <v>-26400</v>
+        <v>-38000</v>
       </c>
       <c r="J94" s="3">
-        <v>-81900</v>
+        <v>-137500</v>
       </c>
       <c r="K94" s="3">
         <v>-6500</v>
@@ -3995,7 +3995,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-636700</v>
+        <v>730000</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -4007,13 +4007,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-89900</v>
+        <v>124400</v>
       </c>
       <c r="I96" s="3">
-        <v>-58400</v>
+        <v>84000</v>
       </c>
       <c r="J96" s="3">
-        <v>-34100</v>
+        <v>57400</v>
       </c>
       <c r="K96" s="3">
         <v>-35900</v>
@@ -4163,25 +4163,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-789900</v>
+        <v>-905700</v>
       </c>
       <c r="E100" s="3">
-        <v>-36000</v>
+        <v>-37900</v>
       </c>
       <c r="F100" s="3">
-        <v>1193300</v>
+        <v>1191600</v>
       </c>
       <c r="G100" s="3">
-        <v>141800</v>
+        <v>151900</v>
       </c>
       <c r="H100" s="3">
-        <v>761000</v>
+        <v>1053300</v>
       </c>
       <c r="I100" s="3">
-        <v>68300</v>
+        <v>98200</v>
       </c>
       <c r="J100" s="3">
-        <v>105100</v>
+        <v>176400</v>
       </c>
       <c r="K100" s="3">
         <v>16900</v>
@@ -4205,25 +4205,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-5100</v>
+        <v>-5800</v>
       </c>
       <c r="E101" s="3">
-        <v>-3000</v>
+        <v>-3200</v>
       </c>
       <c r="F101" s="3">
-        <v>-67700</v>
+        <v>-67600</v>
       </c>
       <c r="G101" s="3">
-        <v>9900</v>
+        <v>10600</v>
       </c>
       <c r="H101" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I101" s="3">
-        <v>2700</v>
+        <v>3900</v>
       </c>
       <c r="J101" s="3">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="K101" s="3">
         <v>-1500</v>
@@ -4247,25 +4247,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>762600</v>
+        <v>874400</v>
       </c>
       <c r="E102" s="3">
-        <v>218500</v>
+        <v>229900</v>
       </c>
       <c r="F102" s="3">
-        <v>196200</v>
+        <v>195900</v>
       </c>
       <c r="G102" s="3">
-        <v>318600</v>
+        <v>341300</v>
       </c>
       <c r="H102" s="3">
-        <v>46900</v>
+        <v>64900</v>
       </c>
       <c r="I102" s="3">
-        <v>-37500</v>
+        <v>-53900</v>
       </c>
       <c r="J102" s="3">
-        <v>71100</v>
+        <v>119400</v>
       </c>
       <c r="K102" s="3">
         <v>9900</v>

--- a/AAII_Financials/Yearly/XP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/XP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="92">
   <si>
     <t>XP</t>
   </si>
@@ -656,58 +656,58 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -717,39 +717,42 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2627600</v>
+      </c>
+      <c r="E8" s="3">
         <v>2935200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2448700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2143200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1559500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1254700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>745500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>557100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>257400</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -759,36 +762,39 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>818600</v>
+      </c>
+      <c r="E9" s="3">
         <v>906600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>732200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>615600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>509400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>397200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>241000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>175100</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -801,36 +807,39 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1809000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2028700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1716400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1527600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1050100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>857500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>504500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>382100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -843,9 +852,12 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,8 +874,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -903,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,81 +961,87 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>25600</v>
+        <v>7800</v>
       </c>
       <c r="E14" s="3">
-        <v>2900</v>
+        <v>16200</v>
       </c>
       <c r="F14" s="3">
+        <v>5600</v>
+      </c>
+      <c r="G14" s="3">
         <v>1400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>18800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>7100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>6200</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E15" s="3">
         <v>21600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>9500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>14900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>16600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>17200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>9800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>6200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4700</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1029,9 +1051,12 @@
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,38 +1070,39 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2113600</v>
+        <v>1821300</v>
       </c>
       <c r="E17" s="3">
-        <v>1791900</v>
+        <v>2123000</v>
       </c>
       <c r="F17" s="3">
+        <v>1789200</v>
+      </c>
+      <c r="G17" s="3">
         <v>1455700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1074700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>865600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>572900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>377200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>180500</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1086,39 +1112,42 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>821600</v>
+        <v>806300</v>
       </c>
       <c r="E18" s="3">
-        <v>656800</v>
+        <v>812200</v>
       </c>
       <c r="F18" s="3">
+        <v>659400</v>
+      </c>
+      <c r="G18" s="3">
         <v>687600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>484900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>389100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>172600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>179900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>76900</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1128,9 +1157,12 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,37 +1179,38 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-15100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
@@ -1188,39 +1221,42 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>858400</v>
+        <v>835500</v>
       </c>
       <c r="E21" s="3">
-        <v>664000</v>
+        <v>849000</v>
       </c>
       <c r="F21" s="3">
+        <v>666600</v>
+      </c>
+      <c r="G21" s="3">
         <v>701100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>501600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>406300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>182400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>186100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>81600</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,9 +1266,12 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1269,42 +1308,45 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>806200</v>
+      </c>
+      <c r="E23" s="3">
         <v>811200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>651600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>684700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>466300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>384100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>165500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>173700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>76900</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1314,39 +1356,42 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>76200</v>
+      </c>
+      <c r="E24" s="3">
         <v>7600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-25600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>40000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>65500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>113100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>45300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>45900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>26800</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1356,9 +1401,12 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,39 +1446,42 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>730000</v>
+      </c>
+      <c r="E26" s="3">
         <v>803600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>677200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>644800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>400800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>271000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>120200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>127900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>50100</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1440,39 +1491,42 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>729800</v>
+      </c>
+      <c r="E27" s="3">
         <v>803500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>677000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>644200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>399800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>268800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>119200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>124900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>38800</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1482,9 +1536,12 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1566,9 +1626,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,38 +1716,41 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E32" s="3">
         <v>15100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
@@ -1692,39 +1761,42 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>729700</v>
+      </c>
+      <c r="E33" s="3">
         <v>803500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>677000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>644200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>399800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>268800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>119200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>124900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>38800</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1734,9 +1806,12 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,39 +1851,42 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>729700</v>
+      </c>
+      <c r="E35" s="3">
         <v>803500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>677000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>644200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>399800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>268800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>119200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>124900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>38800</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1818,44 +1896,47 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1865,9 +1946,12 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,35 +1987,36 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>907100</v>
+      </c>
+      <c r="E41" s="3">
         <v>812700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>672100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>446100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>376400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>27300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>17700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>46300</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1943,36 +2029,39 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>35179300</v>
+      </c>
+      <c r="E42" s="3">
         <v>29087000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>19410700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>13938600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>12209100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>8899300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3715000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1503100</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -1985,36 +2074,39 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4855900</v>
+      </c>
+      <c r="E43" s="3">
         <v>6035100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4318200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2386100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>852900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>119300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>56800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>47200</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2027,9 +2119,12 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2054,8 +2149,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2069,36 +2164,39 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1378000</v>
+      </c>
+      <c r="E45" s="3">
         <v>972400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1120100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>388000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>352400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>257400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>338100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>313100</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2111,36 +2209,39 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>42320300</v>
+      </c>
+      <c r="E46" s="3">
         <v>36907200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>25521100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>17158800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13790900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9303300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4127600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1909700</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2153,33 +2254,36 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>11393500</v>
+      </c>
+      <c r="E47" s="3">
         <v>12001700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9370800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6649000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4166500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1219700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>235400</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2195,36 +2299,39 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>123400</v>
+      </c>
+      <c r="E48" s="3">
         <v>135000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>107700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>107400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>74600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>92000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>25600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14200</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2237,36 +2344,39 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>425900</v>
+      </c>
+      <c r="E49" s="3">
         <v>515600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>159700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>147300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>137400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>137700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>130400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>145900</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2279,9 +2389,12 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,36 +2479,39 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1448100</v>
+      </c>
+      <c r="E52" s="3">
         <v>1331100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>860600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>717600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>224700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>28900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>19900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>16100</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2405,9 +2524,12 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,36 +2569,39 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>56178200</v>
+      </c>
+      <c r="E54" s="3">
         <v>51324300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>36324800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>25008600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>18491300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10852500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4578400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2154200</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2489,9 +2614,12 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,35 +2655,36 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>123400</v>
+      </c>
+      <c r="E57" s="3">
         <v>195400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>116800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>155700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>165500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>66400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>34800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>21600</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2567,36 +2697,39 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>16994300</v>
+        <v>21283600</v>
       </c>
       <c r="E58" s="3">
+        <v>16983100</v>
+      </c>
+      <c r="F58" s="3">
         <v>10577100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7588300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>8117300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5334100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2309200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>496200</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2609,36 +2742,39 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12232100</v>
+      </c>
+      <c r="E59" s="3">
         <v>9333500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7671600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4702700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3981400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2353000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1397400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>994400</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2651,36 +2787,39 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>26828200</v>
+        <v>33890900</v>
       </c>
       <c r="E60" s="3">
+        <v>26817000</v>
+      </c>
+      <c r="F60" s="3">
         <v>18590600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12679700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12426400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7896200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3808100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1567100</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -2693,36 +2832,39 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>4942500</v>
+        <v>4458400</v>
       </c>
       <c r="E61" s="3">
+        <v>4953700</v>
+      </c>
+      <c r="F61" s="3">
         <v>3743900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2724600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>697500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>234000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>214000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>233800</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2735,36 +2877,39 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3837400</v>
+      </c>
+      <c r="E62" s="3">
         <v>3901900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2094700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1281900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>689500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3600</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2777,9 +2922,12 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,36 +3057,39 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>52936900</v>
+      </c>
+      <c r="E66" s="3">
         <v>47315700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>33101100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>22420600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>16392900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9072200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4038100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1806500</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2945,9 +3102,12 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,9 +3301,12 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3155,12 +3328,12 @@
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K72" s="3">
         <v>45400</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3173,9 +3346,12 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,36 +3481,39 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3240700</v>
+      </c>
+      <c r="E76" s="3">
         <v>4008300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3222400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2587500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2097900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1779600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>538500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>345300</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3341,9 +3526,12 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,44 +3571,47 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3430,39 +3621,42 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>729700</v>
+      </c>
+      <c r="E81" s="3">
         <v>803500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>677000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>644200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>399800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>268800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>119200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>124900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>38800</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3472,9 +3666,12 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,38 +3688,39 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E83" s="3">
         <v>24400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>20900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>12300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>13000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>13200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4700</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,9 +3730,12 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,39 +3955,42 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1807500</v>
+      </c>
+      <c r="E89" s="3">
         <v>1674900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>341200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-721600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>290900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-948800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-118000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>79200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1000</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3784,9 +4000,12 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,38 +4022,39 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-24300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-28000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-18000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-21500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-9200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2600</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3844,9 +4064,12 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,39 +4154,42 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-269600</v>
+      </c>
+      <c r="E94" s="3">
         <v>111000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-70200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-206500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-112100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-40200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-38000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-137500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6500</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3970,9 +4199,12 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,17 +4221,18 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>329400</v>
+      </c>
+      <c r="E96" s="3">
         <v>730000</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
@@ -4007,20 +4240,20 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>124400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>84000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>57400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-35900</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -4030,9 +4263,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,39 +4398,42 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-935200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-905700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-37900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1191600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>151900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1053300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>98200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>176400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>16900</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4198,39 +4443,42 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-67600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>10600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1500</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4240,39 +4488,42 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>598100</v>
+      </c>
+      <c r="E102" s="3">
         <v>874400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>229900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>195900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>341300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>64900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-53900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>119400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>9900</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4282,7 +4533,10 @@
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/XP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/XP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="92">
   <si>
     <t>XP</t>
   </si>
@@ -656,61 +656,61 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -720,42 +720,45 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3226800</v>
+      </c>
+      <c r="E8" s="3">
         <v>2627600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2935200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2448700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2143200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1559500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1254700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>745500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>557100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>257400</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -765,39 +768,42 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>991800</v>
+      </c>
+      <c r="E9" s="3">
         <v>818600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>906600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>732200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>615600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>509400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>397200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>241000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>175100</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -810,39 +816,42 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2235000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1809000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2028700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1716400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1527600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1050100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>857500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>504500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>382100</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -855,9 +864,12 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,8 +887,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -919,9 +932,12 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,87 +980,93 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E14" s="3">
         <v>7800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>16200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>18800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>7100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>6200</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E15" s="3">
         <v>21500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>21600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>9500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>14900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>16600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>17200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>9800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>6200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4700</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1054,9 +1076,12 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,41 +1096,42 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2241900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1821300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2123000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1789200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1455700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1074700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>865600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>572900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>377200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>180500</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1115,42 +1141,45 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>984900</v>
+      </c>
+      <c r="E18" s="3">
         <v>806300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>812200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>659400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>687600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>484900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>389100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>172600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>179900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>76900</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1160,9 +1189,12 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,40 +1212,41 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-7600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-15100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
@@ -1224,42 +1257,45 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1039000</v>
+      </c>
+      <c r="E21" s="3">
         <v>835500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>849000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>666600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>701100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>501600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>406300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>182400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>186100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>81600</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1269,9 +1305,12 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1311,45 +1350,48 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>989200</v>
+      </c>
+      <c r="E23" s="3">
         <v>806200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>811200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>651600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>684700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>466300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>384100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>165500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>173700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>76900</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1359,42 +1401,45 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>50700</v>
+      </c>
+      <c r="E24" s="3">
         <v>76200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-25600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>40000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>65500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>113100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>45300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>45900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>26800</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1404,9 +1449,12 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,42 +1497,45 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>938500</v>
+      </c>
+      <c r="E26" s="3">
         <v>730000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>803600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>677200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>644800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>400800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>271000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>120200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>127900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>50100</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1494,42 +1545,45 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>938600</v>
+      </c>
+      <c r="E27" s="3">
         <v>729800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>803500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>677000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>644200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>399800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>268800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>119200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>124900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>38800</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,9 +1593,12 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1629,9 +1689,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,41 +1785,44 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E32" s="3">
         <v>7600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>15100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
@@ -1764,42 +1833,45 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>938600</v>
+      </c>
+      <c r="E33" s="3">
         <v>729700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>803500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>677000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>644200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>399800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>268800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>119200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>124900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>38800</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1809,9 +1881,12 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,42 +1929,45 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>938600</v>
+      </c>
+      <c r="E35" s="3">
         <v>729700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>803500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>677000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>644200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>399800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>268800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>119200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>124900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>38800</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1899,47 +1977,50 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1949,9 +2030,12 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,38 +2073,39 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1880300</v>
+      </c>
+      <c r="E41" s="3">
         <v>907100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>812700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>672100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>446100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>376400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>27300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>17700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>46300</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2032,39 +2118,42 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>46542200</v>
+      </c>
+      <c r="E42" s="3">
         <v>35179300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>29087000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>19410700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>13938600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>12209100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>8899300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3715000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1503100</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2077,39 +2166,42 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6451700</v>
+      </c>
+      <c r="E43" s="3">
         <v>4855900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6035100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4318200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2386100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>852900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>119300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>56800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>47200</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,9 +2214,12 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2152,8 +2247,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2167,39 +2262,42 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1477400</v>
+      </c>
+      <c r="E45" s="3">
         <v>1378000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>972400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1120100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>388000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>352400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>257400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>338100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>313100</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2212,39 +2310,42 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>56351700</v>
+      </c>
+      <c r="E46" s="3">
         <v>42320300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>36907200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>25521100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>17158800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13790900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9303300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4127600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1909700</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2257,36 +2358,39 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>12741200</v>
+      </c>
+      <c r="E47" s="3">
         <v>11393500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>12001700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9370800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6649000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4166500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1219700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>235400</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2302,39 +2406,42 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>146000</v>
+      </c>
+      <c r="E48" s="3">
         <v>123400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>135000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>107700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>107400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>74600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>92000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>25600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14200</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2347,39 +2454,42 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>501700</v>
+      </c>
+      <c r="E49" s="3">
         <v>425900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>515600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>159700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>147300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>137400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>137700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>130400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>145900</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2392,9 +2502,12 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,39 +2598,42 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1638800</v>
+      </c>
+      <c r="E52" s="3">
         <v>1448100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1331100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>860600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>717600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>224700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>28900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>19900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16100</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2527,9 +2646,12 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,39 +2694,42 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>71991300</v>
+      </c>
+      <c r="E54" s="3">
         <v>56178200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>51324300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>36324800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>25008600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>18491300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10852500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4578400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2154200</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2617,9 +2742,12 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,38 +2785,39 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>147100</v>
+      </c>
+      <c r="E57" s="3">
         <v>123400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>195400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>116800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>155700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>165500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>66400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>34800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>21600</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2700,39 +2830,42 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>23133500</v>
+      </c>
+      <c r="E58" s="3">
         <v>21283600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>16983100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10577100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7588300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>8117300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5334100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2309200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>496200</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2745,39 +2878,42 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>18459300</v>
+      </c>
+      <c r="E59" s="3">
         <v>12232100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9333500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7671600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4702700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3981400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2353000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1397400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>994400</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2790,39 +2926,42 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>42044100</v>
+      </c>
+      <c r="E60" s="3">
         <v>33890900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>26817000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>18590600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12679700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12426400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7896200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3808100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1567100</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -2835,39 +2974,42 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3851400</v>
+      </c>
+      <c r="E61" s="3">
         <v>4458400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4953700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3743900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2724600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>697500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>234000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>214000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>233800</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2880,39 +3022,42 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4843000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3837400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3901900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2094700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1281900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>689500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3600</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2925,9 +3070,12 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,39 +3214,42 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>67716200</v>
+      </c>
+      <c r="E66" s="3">
         <v>52936900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>47315700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>33101100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>22420600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16392900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9072200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4038100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1806500</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3105,9 +3262,12 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3259,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,9 +3474,12 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3331,12 +3504,12 @@
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L72" s="3">
         <v>45400</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,9 +3522,12 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,39 +3666,42 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4275000</v>
+      </c>
+      <c r="E76" s="3">
         <v>3240700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4008300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3222400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2587500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2097900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1779600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>538500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>345300</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3529,9 +3714,12 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,47 +3762,50 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3624,42 +3815,45 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>938600</v>
+      </c>
+      <c r="E81" s="3">
         <v>729700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>803500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>677000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>644200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>399800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>268800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>119200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>124900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>38800</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3669,9 +3863,12 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,41 +3886,42 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E83" s="3">
         <v>20200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>24400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>20900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>12300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>13000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>13200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4700</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3733,9 +3931,12 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,42 +4171,45 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2186800</v>
+      </c>
+      <c r="E89" s="3">
         <v>1807500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1674900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>341200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-721600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>290900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-948800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-118000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>79200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1000</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4003,9 +4219,12 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,41 +4242,42 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-23400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-24300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-28000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-18000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-21500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-9200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2600</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4067,9 +4287,12 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,42 +4383,45 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-130000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-269600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>111000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-70200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-206500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-112100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-40200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-38000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-137500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6500</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4202,9 +4431,12 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,20 +4454,21 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>89800</v>
+      </c>
+      <c r="E96" s="3">
         <v>329400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>730000</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
@@ -4243,20 +4476,20 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>124400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>84000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>57400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-35900</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -4266,9 +4499,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,42 +4643,45 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-894600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-935200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-905700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-37900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1191600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>151900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1053300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>98200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>176400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>16900</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4446,42 +4691,45 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-5800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-3200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-67600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>10600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1500</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4491,42 +4739,45 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1145800</v>
+      </c>
+      <c r="E102" s="3">
         <v>598100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>874400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>229900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>195900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>341300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>64900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-53900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>119400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>9900</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4536,7 +4787,10 @@
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
